--- a/SourceFiles/DeedInfo-3-Hobbies.xlsx
+++ b/SourceFiles/DeedInfo-3-Hobbies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkckx\Documents\The Lord of the Rings Online\Plugins\CubePlugins\DeedTracker\SourceFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83090C1B-D964-415A-A9A7-2D38985E9338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7CF0A0D-3990-4582-A8F4-C316E1F42EDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{CDC9C16A-58F0-4807-B5CD-F77FF9D2EA43}"/>
+    <workbookView xWindow="1290" yWindow="1860" windowWidth="19665" windowHeight="12690" activeTab="6" xr2:uid="{CDC9C16A-58F0-4807-B5CD-F77FF9D2EA43}"/>
   </bookViews>
   <sheets>
     <sheet name="Type" sheetId="2" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="Race" sheetId="8" r:id="rId4"/>
     <sheet name="Vocation" sheetId="5" r:id="rId5"/>
     <sheet name="Fishing" sheetId="11" r:id="rId6"/>
-    <sheet name="&lt;template&gt;" sheetId="1" r:id="rId7"/>
+    <sheet name="Birding" sheetId="12" r:id="rId7"/>
+    <sheet name="&lt;template&gt;" sheetId="1" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="231">
   <si>
     <t>TITLE</t>
   </si>
@@ -550,6 +551,189 @@
   </si>
   <si>
     <t>Minimal</t>
+  </si>
+  <si>
+    <t>All the Birds of Bree-land</t>
+  </si>
+  <si>
+    <t>Birds of Bree-land: Common and Uncommon</t>
+  </si>
+  <si>
+    <t>Birds of Bree-land: Rare</t>
+  </si>
+  <si>
+    <t>The Rarest Bird in Bree-land</t>
+  </si>
+  <si>
+    <t>All the Birds of the Shire</t>
+  </si>
+  <si>
+    <t>The Rarest Bird in The Shire</t>
+  </si>
+  <si>
+    <t>Birds of The Shire: Rare</t>
+  </si>
+  <si>
+    <t>Birds of The Shire: Common and Uncommon</t>
+  </si>
+  <si>
+    <t>All the Birds of Ered Luin</t>
+  </si>
+  <si>
+    <t>The Rarest Bird in Ered Luin</t>
+  </si>
+  <si>
+    <t>Birds of Ered Luin: Rare</t>
+  </si>
+  <si>
+    <t>Birds of Ered Luin: Common and Uncommon</t>
+  </si>
+  <si>
+    <t>All the Birds of Swanfleet</t>
+  </si>
+  <si>
+    <t>Birds of Swanfleet: Common and Uncommon</t>
+  </si>
+  <si>
+    <t>Birds of Swanfleet: Rare</t>
+  </si>
+  <si>
+    <t>The Rarest Bird in Swanfleet</t>
+  </si>
+  <si>
+    <t>All the Birds of the Lone-lands</t>
+  </si>
+  <si>
+    <t>Birds of the Lone-lands: Common and Uncommon</t>
+  </si>
+  <si>
+    <t>Birds of the Lone-lands: Rare</t>
+  </si>
+  <si>
+    <t>The Rarest Bird in the Lone-lands</t>
+  </si>
+  <si>
+    <t>All the Birds of the North Downs</t>
+  </si>
+  <si>
+    <t>Birds of The North Downs: Common and Uncommon</t>
+  </si>
+  <si>
+    <t>Birds of the North Downs: Rare</t>
+  </si>
+  <si>
+    <t>The Rarest Bird in the North Downs</t>
+  </si>
+  <si>
+    <t>All the Birds of the Trollshaws</t>
+  </si>
+  <si>
+    <t>Birds of the Trollshaws: Common and Uncommon</t>
+  </si>
+  <si>
+    <t>Birds of the Trollshaws: Rare</t>
+  </si>
+  <si>
+    <t>The Rarest Bird in the Trollshaws</t>
+  </si>
+  <si>
+    <t>All the Birds of the Misty Mountains</t>
+  </si>
+  <si>
+    <t>Birds of the Misty Mountains: Common and Uncommon</t>
+  </si>
+  <si>
+    <t>Birds of the Misty Mountains: Rare</t>
+  </si>
+  <si>
+    <t>The Rarest Bird in the Misty Mountains</t>
+  </si>
+  <si>
+    <t>All the Birds of Evendim</t>
+  </si>
+  <si>
+    <t>Birds of Evendim: Common and Uncommon</t>
+  </si>
+  <si>
+    <t>Birds of Evendim: Rare</t>
+  </si>
+  <si>
+    <t>The Rarest Bird in Evendim</t>
+  </si>
+  <si>
+    <t>All the Birds of Angmar</t>
+  </si>
+  <si>
+    <t>Birds of Angmar: Common and Uncommon</t>
+  </si>
+  <si>
+    <t>Birds of Angmar: Rare</t>
+  </si>
+  <si>
+    <t>The Rarest Bird in Angmar</t>
+  </si>
+  <si>
+    <t>All the Birds of Forochel</t>
+  </si>
+  <si>
+    <t>Birds of Forochel: Common and Uncommon</t>
+  </si>
+  <si>
+    <t>Birds of Forochel: Rare</t>
+  </si>
+  <si>
+    <t>The Rarest Bird in Forochel</t>
+  </si>
+  <si>
+    <t>All the Birds of Eregion</t>
+  </si>
+  <si>
+    <t>Birds of Eregion: Common and Uncommon</t>
+  </si>
+  <si>
+    <t>Birds of Eregion: Rare</t>
+  </si>
+  <si>
+    <t>The Rarest Bird in Eregion</t>
+  </si>
+  <si>
+    <t>All the Birds of Enedwaith</t>
+  </si>
+  <si>
+    <t>Birds of Enedwaith: Common and Uncommon</t>
+  </si>
+  <si>
+    <t>Birds of Enedwaith: Rare</t>
+  </si>
+  <si>
+    <t>The Rarest Bird in Enedwaith</t>
+  </si>
+  <si>
+    <t>All the Birds of Dunland</t>
+  </si>
+  <si>
+    <t>Birds of Dunland: Common and Uncommon</t>
+  </si>
+  <si>
+    <t>Birds of Dunland: Rare</t>
+  </si>
+  <si>
+    <t>The Rarest Bird in Dunland</t>
+  </si>
+  <si>
+    <t>All the Birds of Cardolan</t>
+  </si>
+  <si>
+    <t>Birds of Cardolan: Common and Uncommon</t>
+  </si>
+  <si>
+    <t>Birds of Cardolan: Rare</t>
+  </si>
+  <si>
+    <t>The Rarest Bird in Cardolan</t>
+  </si>
+  <si>
+    <t>The Rarest of Birds in Eriador</t>
   </si>
 </sst>
 </file>
@@ -607,7 +791,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -642,9 +836,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -682,7 +876,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -788,7 +982,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -930,7 +1124,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2124,7 +2318,7 @@
         <v xml:space="preserve">  [1] = {["ID"] = 1879115029; }; -- Darter-master</v>
       </c>
       <c r="P2" s="1" t="str">
-        <f>CONCATENATE(R2,S2,V2,X2,Z2,AB2,AD2,AF2,AG2,AH2,AI2,AJ2,AK2,AL2)</f>
+        <f t="shared" ref="P2:P7" si="0">CONCATENATE(R2,S2,V2,X2,Z2,AB2,AD2,AF2,AG2,AH2,AI2,AJ2,AK2,AL2)</f>
         <v xml:space="preserve">  [1] = {["ID"] = 1879115029; ["SAVE_INDEX"] = 1; ["TYPE"] =  7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Darter-master"; }; ["LORE"] = { ["EN"] = "Catching all nine darters is no easy task!"; }; ["SUMMARY"] = { ["EN"] = "Catch all 9 Darter varieties"; }; ["TITLE"] = { ["EN"] = "Darter-master"; }; };</v>
       </c>
       <c r="Q2">
@@ -2136,19 +2330,19 @@
         <v xml:space="preserve">  [1] = {</v>
       </c>
       <c r="S2" t="str">
-        <f>IF(LEN(A2)&gt;0,CONCATENATE("[""ID""] = ",A2,"; "),"                     ")</f>
+        <f t="shared" ref="S2:S7" si="1">IF(LEN(A2)&gt;0,CONCATENATE("[""ID""] = ",A2,"; "),"                     ")</f>
         <v xml:space="preserve">["ID"] = 1879115029; </v>
       </c>
       <c r="T2" t="str">
-        <f>IF(LEN(A2)&gt;0,CONCATENATE("[""ID""] = ",A2,"; "),"")</f>
+        <f t="shared" ref="T2:T7" si="2">IF(LEN(A2)&gt;0,CONCATENATE("[""ID""] = ",A2,"; "),"")</f>
         <v xml:space="preserve">["ID"] = 1879115029; </v>
       </c>
       <c r="U2" t="str">
-        <f>IF(LEN(M2)&gt;0,CONCATENATE("[""CAT_ID""] = ",M2,"; "),"")</f>
+        <f t="shared" ref="U2:U7" si="3">IF(LEN(M2)&gt;0,CONCATENATE("[""CAT_ID""] = ",M2,"; "),"")</f>
         <v/>
       </c>
       <c r="V2" s="1" t="str">
-        <f>IF(LEN(B2)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B2)),B2,"; "),"")</f>
+        <f t="shared" ref="V2:V7" si="4">IF(LEN(B2)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B2)),B2,"; "),"")</f>
         <v xml:space="preserve">["SAVE_INDEX"] = 1; </v>
       </c>
       <c r="W2">
@@ -2160,7 +2354,7 @@
         <v xml:space="preserve">["TYPE"] =  7; </v>
       </c>
       <c r="Y2" t="str">
-        <f>TEXT(E2,0)</f>
+        <f t="shared" ref="Y2:Y7" si="5">TEXT(E2,0)</f>
         <v>0</v>
       </c>
       <c r="Z2" t="str">
@@ -2168,7 +2362,7 @@
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AA2" t="str">
-        <f>TEXT(G2,0)</f>
+        <f t="shared" ref="AA2:AA7" si="6">TEXT(G2,0)</f>
         <v>0</v>
       </c>
       <c r="AB2" t="str">
@@ -2176,7 +2370,7 @@
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AC2" t="str">
-        <f>TEXT(H2,0)</f>
+        <f t="shared" ref="AC2:AC7" si="7">TEXT(H2,0)</f>
         <v>0</v>
       </c>
       <c r="AD2" t="str">
@@ -2188,7 +2382,7 @@
         <v>1</v>
       </c>
       <c r="AF2" t="str">
-        <f t="shared" ref="AF2" si="0">CONCATENATE("[""FACTION""] = ",TEXT(AE2,"0"),"; ")</f>
+        <f t="shared" ref="AF2" si="8">CONCATENATE("[""FACTION""] = ",TEXT(AE2,"0"),"; ")</f>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AG2" t="str">
@@ -2245,35 +2439,35 @@
         <v>0</v>
       </c>
       <c r="O3" t="str">
-        <f t="shared" ref="O3:O7" si="1">CONCATENATE(R3,T3,U3,AL3," -- ",C3)</f>
+        <f t="shared" ref="O3:O7" si="9">CONCATENATE(R3,T3,U3,AL3," -- ",C3)</f>
         <v xml:space="preserve">  [2] = {["ID"] = 1879206842; }; -- Fortunate Festival Fishes</v>
       </c>
       <c r="P3" s="1" t="str">
-        <f>CONCATENATE(R3,S3,V3,X3,Z3,AB3,AD3,AF3,AG3,AH3,AI3,AJ3,AK3,AL3)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">  [2] = {["ID"] = 1879206842; ["SAVE_INDEX"] = 2; ["TYPE"] = 12; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Fortunate Festival Fishes"; }; ["LORE"] = { ["EN"] = "You catch many rare and wondrous fish during the Summer Festival."; }; ["SUMMARY"] = { ["EN"] = "Catch 10 of 4 types of fish during summer-festival"; }; ["TITLE"] = { ["EN"] = "Rare Fish"; }; };</v>
       </c>
       <c r="Q3">
-        <f t="shared" ref="Q3:Q7" si="2">ROW()-1</f>
+        <f t="shared" ref="Q3:Q7" si="10">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="R3" t="str">
-        <f t="shared" ref="R3:R7" si="3">CONCATENATE(REPT(" ",3-LEN(Q3)),"[",Q3,"] = {")</f>
+        <f t="shared" ref="R3:R7" si="11">CONCATENATE(REPT(" ",3-LEN(Q3)),"[",Q3,"] = {")</f>
         <v xml:space="preserve">  [2] = {</v>
       </c>
       <c r="S3" t="str">
-        <f>IF(LEN(A3)&gt;0,CONCATENATE("[""ID""] = ",A3,"; "),"                     ")</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve">["ID"] = 1879206842; </v>
       </c>
       <c r="T3" t="str">
-        <f>IF(LEN(A3)&gt;0,CONCATENATE("[""ID""] = ",A3,"; "),"")</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve">["ID"] = 1879206842; </v>
       </c>
       <c r="U3" t="str">
-        <f>IF(LEN(M3)&gt;0,CONCATENATE("[""CAT_ID""] = ",M3,"; "),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="V3" s="1" t="str">
-        <f>IF(LEN(B3)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B3)),B3,"; "),"")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">["SAVE_INDEX"] = 2; </v>
       </c>
       <c r="W3">
@@ -2281,31 +2475,31 @@
         <v>12</v>
       </c>
       <c r="X3" t="str">
-        <f t="shared" ref="X3:X7" si="4">CONCATENATE("[""TYPE""] = ",REPT(" ",2-LEN(W3)),W3,"; ")</f>
+        <f t="shared" ref="X3:X7" si="12">CONCATENATE("[""TYPE""] = ",REPT(" ",2-LEN(W3)),W3,"; ")</f>
         <v xml:space="preserve">["TYPE"] = 12; </v>
       </c>
       <c r="Y3" t="str">
-        <f>TEXT(E3,0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z3" t="str">
-        <f t="shared" ref="Z3:Z7" si="5">CONCATENATE("[""VXP""] = ",REPT(" ",1-LEN(Y3)),TEXT(Y3,"0"),"; ")</f>
+        <f t="shared" ref="Z3:Z7" si="13">CONCATENATE("[""VXP""] = ",REPT(" ",1-LEN(Y3)),TEXT(Y3,"0"),"; ")</f>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AA3" t="str">
-        <f>TEXT(G3,0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AB3" t="str">
-        <f t="shared" ref="AB3:AB7" si="6">CONCATENATE("[""LP""] = ",REPT(" ",1-LEN(AA3)),TEXT(AA3,"0"),"; ")</f>
+        <f t="shared" ref="AB3:AB7" si="14">CONCATENATE("[""LP""] = ",REPT(" ",1-LEN(AA3)),TEXT(AA3,"0"),"; ")</f>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AC3" t="str">
-        <f>TEXT(H3,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AD3" t="str">
-        <f t="shared" ref="AD3:AD7" si="7">CONCATENATE("[""REP""] = ",REPT(" ",1-LEN(AC3)),TEXT(AC3,"0"),"; ")</f>
+        <f t="shared" ref="AD3:AD7" si="15">CONCATENATE("[""REP""] = ",REPT(" ",1-LEN(AC3)),TEXT(AC3,"0"),"; ")</f>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AE3">
@@ -2313,31 +2507,31 @@
         <v>1</v>
       </c>
       <c r="AF3" t="str">
-        <f t="shared" ref="AF3:AF7" si="8">CONCATENATE("[""FACTION""] = ",TEXT(AE3,"0"),"; ")</f>
+        <f t="shared" ref="AF3:AF7" si="16">CONCATENATE("[""FACTION""] = ",TEXT(AE3,"0"),"; ")</f>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AG3" t="str">
-        <f t="shared" ref="AG3:AG7" si="9">CONCATENATE("[""TIER""] = ",TEXT(L3,"0"),"; ")</f>
+        <f t="shared" ref="AG3:AG7" si="17">CONCATENATE("[""TIER""] = ",TEXT(L3,"0"),"; ")</f>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AH3" t="str">
-        <f t="shared" ref="AH3:AH7" si="10">CONCATENATE("[""NAME""] = { [""EN""] = """,C3,"""; }; ")</f>
+        <f t="shared" ref="AH3:AH7" si="18">CONCATENATE("[""NAME""] = { [""EN""] = """,C3,"""; }; ")</f>
         <v xml:space="preserve">["NAME"] = { ["EN"] = "Fortunate Festival Fishes"; }; </v>
       </c>
       <c r="AI3" t="str">
-        <f t="shared" ref="AI3:AI7" si="11">CONCATENATE("[""LORE""] = { [""EN""] = """,K3,"""; }; ")</f>
+        <f t="shared" ref="AI3:AI7" si="19">CONCATENATE("[""LORE""] = { [""EN""] = """,K3,"""; }; ")</f>
         <v xml:space="preserve">["LORE"] = { ["EN"] = "You catch many rare and wondrous fish during the Summer Festival."; }; </v>
       </c>
       <c r="AJ3" t="str">
-        <f t="shared" ref="AJ3:AJ7" si="12">CONCATENATE("[""SUMMARY""] = { [""EN""] = """,J3,"""; }; ")</f>
+        <f t="shared" ref="AJ3:AJ7" si="20">CONCATENATE("[""SUMMARY""] = { [""EN""] = """,J3,"""; }; ")</f>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = "Catch 10 of 4 types of fish during summer-festival"; }; </v>
       </c>
       <c r="AK3" t="str">
-        <f t="shared" ref="AK3:AK7" si="13">IF(LEN(F3)&gt;0,CONCATENATE("[""TITLE""] = { [""EN""] = """,F3,"""; }; "),"")</f>
+        <f t="shared" ref="AK3:AK7" si="21">IF(LEN(F3)&gt;0,CONCATENATE("[""TITLE""] = { [""EN""] = """,F3,"""; }; "),"")</f>
         <v xml:space="preserve">["TITLE"] = { ["EN"] = "Rare Fish"; }; </v>
       </c>
       <c r="AL3" t="str">
-        <f t="shared" ref="AL3:AL7" si="14">CONCATENATE("};")</f>
+        <f t="shared" ref="AL3:AL7" si="22">CONCATENATE("};")</f>
         <v>};</v>
       </c>
     </row>
@@ -2370,35 +2564,35 @@
         <v>0</v>
       </c>
       <c r="O4" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">  [3] = {["ID"] = 1879115020; }; -- Sturgeon-master</v>
+      </c>
+      <c r="P4" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  [3] = {["ID"] = 1879115020; ["SAVE_INDEX"] = 3; ["TYPE"] =  7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Sturgeon-master"; }; ["LORE"] = { ["EN"] = "Catching nine types of sturgeon will not be easy!"; }; ["SUMMARY"] = { ["EN"] = "Catch all 9 Sturgeon varieties"; }; ["TITLE"] = { ["EN"] = "Sturgeon-master"; }; };</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="R4" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">  [3] = {</v>
+      </c>
+      <c r="S4" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">  [3] = {["ID"] = 1879115020; }; -- Sturgeon-master</v>
-      </c>
-      <c r="P4" s="1" t="str">
-        <f>CONCATENATE(R4,S4,V4,X4,Z4,AB4,AD4,AF4,AG4,AH4,AI4,AJ4,AK4,AL4)</f>
-        <v xml:space="preserve">  [3] = {["ID"] = 1879115020; ["SAVE_INDEX"] = 3; ["TYPE"] =  7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Sturgeon-master"; }; ["LORE"] = { ["EN"] = "Catching nine types of sturgeon will not be easy!"; }; ["SUMMARY"] = { ["EN"] = "Catch all 9 Sturgeon varieties"; }; ["TITLE"] = { ["EN"] = "Sturgeon-master"; }; };</v>
-      </c>
-      <c r="Q4">
+        <v xml:space="preserve">["ID"] = 1879115020; </v>
+      </c>
+      <c r="T4" t="str">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="R4" t="str">
+        <v xml:space="preserve">["ID"] = 1879115020; </v>
+      </c>
+      <c r="U4" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">  [3] = {</v>
-      </c>
-      <c r="S4" t="str">
-        <f>IF(LEN(A4)&gt;0,CONCATENATE("[""ID""] = ",A4,"; "),"                     ")</f>
-        <v xml:space="preserve">["ID"] = 1879115020; </v>
-      </c>
-      <c r="T4" t="str">
-        <f>IF(LEN(A4)&gt;0,CONCATENATE("[""ID""] = ",A4,"; "),"")</f>
-        <v xml:space="preserve">["ID"] = 1879115020; </v>
-      </c>
-      <c r="U4" t="str">
-        <f>IF(LEN(M4)&gt;0,CONCATENATE("[""CAT_ID""] = ",M4,"; "),"")</f>
         <v/>
       </c>
       <c r="V4" s="1" t="str">
-        <f>IF(LEN(B4)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B4)),B4,"; "),"")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">["SAVE_INDEX"] = 3; </v>
       </c>
       <c r="W4">
@@ -2406,31 +2600,31 @@
         <v>7</v>
       </c>
       <c r="X4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">["TYPE"] =  7; </v>
       </c>
       <c r="Y4" t="str">
-        <f>TEXT(E4,0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AA4" t="str">
-        <f>TEXT(G4,0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AB4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AC4" t="str">
-        <f>TEXT(H4,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AD4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AE4">
@@ -2438,31 +2632,31 @@
         <v>1</v>
       </c>
       <c r="AF4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AG4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AH4" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">["NAME"] = { ["EN"] = "Sturgeon-master"; }; </v>
       </c>
       <c r="AI4" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v xml:space="preserve">["LORE"] = { ["EN"] = "Catching nine types of sturgeon will not be easy!"; }; </v>
       </c>
       <c r="AJ4" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = "Catch all 9 Sturgeon varieties"; }; </v>
       </c>
       <c r="AK4" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">["TITLE"] = { ["EN"] = "Sturgeon-master"; }; </v>
       </c>
       <c r="AL4" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>};</v>
       </c>
     </row>
@@ -2495,35 +2689,35 @@
         <v>0</v>
       </c>
       <c r="O5" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">  [4] = {["ID"] = 1879110873; }; -- The Salmon King</v>
+      </c>
+      <c r="P5" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  [4] = {["ID"] = 1879110873; ["SAVE_INDEX"] = 4; ["TYPE"] =  7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "The Salmon King"; }; ["LORE"] = { ["EN"] = "Only the most skilled - and lucky - fisher can make a catch of this size!"; }; ["SUMMARY"] = { ["EN"] = "Catch a 50-pound Salmon"; }; ["TITLE"] = { ["EN"] = "the Complete Angler"; }; };</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="R5" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">  [4] = {</v>
+      </c>
+      <c r="S5" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">  [4] = {["ID"] = 1879110873; }; -- The Salmon King</v>
-      </c>
-      <c r="P5" s="1" t="str">
-        <f>CONCATENATE(R5,S5,V5,X5,Z5,AB5,AD5,AF5,AG5,AH5,AI5,AJ5,AK5,AL5)</f>
-        <v xml:space="preserve">  [4] = {["ID"] = 1879110873; ["SAVE_INDEX"] = 4; ["TYPE"] =  7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "The Salmon King"; }; ["LORE"] = { ["EN"] = "Only the most skilled - and lucky - fisher can make a catch of this size!"; }; ["SUMMARY"] = { ["EN"] = "Catch a 50-pound Salmon"; }; ["TITLE"] = { ["EN"] = "the Complete Angler"; }; };</v>
-      </c>
-      <c r="Q5">
+        <v xml:space="preserve">["ID"] = 1879110873; </v>
+      </c>
+      <c r="T5" t="str">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="R5" t="str">
+        <v xml:space="preserve">["ID"] = 1879110873; </v>
+      </c>
+      <c r="U5" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">  [4] = {</v>
-      </c>
-      <c r="S5" t="str">
-        <f>IF(LEN(A5)&gt;0,CONCATENATE("[""ID""] = ",A5,"; "),"                     ")</f>
-        <v xml:space="preserve">["ID"] = 1879110873; </v>
-      </c>
-      <c r="T5" t="str">
-        <f>IF(LEN(A5)&gt;0,CONCATENATE("[""ID""] = ",A5,"; "),"")</f>
-        <v xml:space="preserve">["ID"] = 1879110873; </v>
-      </c>
-      <c r="U5" t="str">
-        <f>IF(LEN(M5)&gt;0,CONCATENATE("[""CAT_ID""] = ",M5,"; "),"")</f>
         <v/>
       </c>
       <c r="V5" s="1" t="str">
-        <f>IF(LEN(B5)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B5)),B5,"; "),"")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">["SAVE_INDEX"] = 4; </v>
       </c>
       <c r="W5">
@@ -2531,31 +2725,31 @@
         <v>7</v>
       </c>
       <c r="X5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">["TYPE"] =  7; </v>
       </c>
       <c r="Y5" t="str">
-        <f>TEXT(E5,0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AA5" t="str">
-        <f>TEXT(G5,0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AB5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AC5" t="str">
-        <f>TEXT(H5,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AD5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AE5">
@@ -2563,31 +2757,31 @@
         <v>1</v>
       </c>
       <c r="AF5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AG5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AH5" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">["NAME"] = { ["EN"] = "The Salmon King"; }; </v>
       </c>
       <c r="AI5" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v xml:space="preserve">["LORE"] = { ["EN"] = "Only the most skilled - and lucky - fisher can make a catch of this size!"; }; </v>
       </c>
       <c r="AJ5" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = "Catch a 50-pound Salmon"; }; </v>
       </c>
       <c r="AK5" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">["TITLE"] = { ["EN"] = "the Complete Angler"; }; </v>
       </c>
       <c r="AL5" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>};</v>
       </c>
     </row>
@@ -2620,35 +2814,35 @@
         <v>0</v>
       </c>
       <c r="O6" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">  [5] = {["ID"] = 1879115023; }; -- Trout-master</v>
+      </c>
+      <c r="P6" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  [5] = {["ID"] = 1879115023; ["SAVE_INDEX"] = 5; ["TYPE"] =  7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Trout-master"; }; ["LORE"] = { ["EN"] = "Find and catch all nine types of trout!"; }; ["SUMMARY"] = { ["EN"] = "Catch all 9 Trout varieties"; }; ["TITLE"] = { ["EN"] = "Trout-master"; }; };</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="10"/>
+        <v>5</v>
+      </c>
+      <c r="R6" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">  [5] = {</v>
+      </c>
+      <c r="S6" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">  [5] = {["ID"] = 1879115023; }; -- Trout-master</v>
-      </c>
-      <c r="P6" s="1" t="str">
-        <f>CONCATENATE(R6,S6,V6,X6,Z6,AB6,AD6,AF6,AG6,AH6,AI6,AJ6,AK6,AL6)</f>
-        <v xml:space="preserve">  [5] = {["ID"] = 1879115023; ["SAVE_INDEX"] = 5; ["TYPE"] =  7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Trout-master"; }; ["LORE"] = { ["EN"] = "Find and catch all nine types of trout!"; }; ["SUMMARY"] = { ["EN"] = "Catch all 9 Trout varieties"; }; ["TITLE"] = { ["EN"] = "Trout-master"; }; };</v>
-      </c>
-      <c r="Q6">
+        <v xml:space="preserve">["ID"] = 1879115023; </v>
+      </c>
+      <c r="T6" t="str">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="R6" t="str">
+        <v xml:space="preserve">["ID"] = 1879115023; </v>
+      </c>
+      <c r="U6" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">  [5] = {</v>
-      </c>
-      <c r="S6" t="str">
-        <f>IF(LEN(A6)&gt;0,CONCATENATE("[""ID""] = ",A6,"; "),"                     ")</f>
-        <v xml:space="preserve">["ID"] = 1879115023; </v>
-      </c>
-      <c r="T6" t="str">
-        <f>IF(LEN(A6)&gt;0,CONCATENATE("[""ID""] = ",A6,"; "),"")</f>
-        <v xml:space="preserve">["ID"] = 1879115023; </v>
-      </c>
-      <c r="U6" t="str">
-        <f>IF(LEN(M6)&gt;0,CONCATENATE("[""CAT_ID""] = ",M6,"; "),"")</f>
         <v/>
       </c>
       <c r="V6" s="1" t="str">
-        <f>IF(LEN(B6)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B6)),B6,"; "),"")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">["SAVE_INDEX"] = 5; </v>
       </c>
       <c r="W6">
@@ -2656,31 +2850,31 @@
         <v>7</v>
       </c>
       <c r="X6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">["TYPE"] =  7; </v>
       </c>
       <c r="Y6" t="str">
-        <f>TEXT(E6,0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AA6" t="str">
-        <f>TEXT(G6,0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AB6" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AC6" t="str">
-        <f>TEXT(H6,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AD6" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AE6">
@@ -2688,31 +2882,31 @@
         <v>1</v>
       </c>
       <c r="AF6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AG6" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AH6" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">["NAME"] = { ["EN"] = "Trout-master"; }; </v>
       </c>
       <c r="AI6" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v xml:space="preserve">["LORE"] = { ["EN"] = "Find and catch all nine types of trout!"; }; </v>
       </c>
       <c r="AJ6" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = "Catch all 9 Trout varieties"; }; </v>
       </c>
       <c r="AK6" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v xml:space="preserve">["TITLE"] = { ["EN"] = "Trout-master"; }; </v>
       </c>
       <c r="AL6" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>};</v>
       </c>
     </row>
@@ -2745,35 +2939,35 @@
         <v>0</v>
       </c>
       <c r="O7" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">  [6] = {["ID"] = 1879364959; }; -- Lake-master</v>
+      </c>
+      <c r="P7" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  [6] = {["ID"] = 1879364959; ["SAVE_INDEX"] = 6; ["TYPE"] =  7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Lake-master"; }; ["LORE"] = { ["EN"] = "Find and catch all twenty types of eastern, freshwater fish!"; }; ["SUMMARY"] = { ["EN"] = "Catch all 20 fish varieties in Lake-town"; }; ["TITLE"] = { ["EN"] = "Lake-master"; }; };</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="10"/>
+        <v>6</v>
+      </c>
+      <c r="R7" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve">  [6] = {</v>
+      </c>
+      <c r="S7" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">  [6] = {["ID"] = 1879364959; }; -- Lake-master</v>
-      </c>
-      <c r="P7" s="1" t="str">
-        <f>CONCATENATE(R7,S7,V7,X7,Z7,AB7,AD7,AF7,AG7,AH7,AI7,AJ7,AK7,AL7)</f>
-        <v xml:space="preserve">  [6] = {["ID"] = 1879364959; ["SAVE_INDEX"] = 6; ["TYPE"] =  7; ["VXP"] = 0; ["LP"] = 0; ["REP"] = 0; ["FACTION"] = 1; ["TIER"] = 0; ["NAME"] = { ["EN"] = "Lake-master"; }; ["LORE"] = { ["EN"] = "Find and catch all twenty types of eastern, freshwater fish!"; }; ["SUMMARY"] = { ["EN"] = "Catch all 20 fish varieties in Lake-town"; }; ["TITLE"] = { ["EN"] = "Lake-master"; }; };</v>
-      </c>
-      <c r="Q7">
+        <v xml:space="preserve">["ID"] = 1879364959; </v>
+      </c>
+      <c r="T7" t="str">
         <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="R7" t="str">
+        <v xml:space="preserve">["ID"] = 1879364959; </v>
+      </c>
+      <c r="U7" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">  [6] = {</v>
-      </c>
-      <c r="S7" t="str">
-        <f>IF(LEN(A7)&gt;0,CONCATENATE("[""ID""] = ",A7,"; "),"                     ")</f>
-        <v xml:space="preserve">["ID"] = 1879364959; </v>
-      </c>
-      <c r="T7" t="str">
-        <f>IF(LEN(A7)&gt;0,CONCATENATE("[""ID""] = ",A7,"; "),"")</f>
-        <v xml:space="preserve">["ID"] = 1879364959; </v>
-      </c>
-      <c r="U7" t="str">
-        <f>IF(LEN(M7)&gt;0,CONCATENATE("[""CAT_ID""] = ",M7,"; "),"")</f>
         <v/>
       </c>
       <c r="V7" s="1" t="str">
-        <f>IF(LEN(B7)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B7)),B7,"; "),"")</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve">["SAVE_INDEX"] = 6; </v>
       </c>
       <c r="W7">
@@ -2781,31 +2975,31 @@
         <v>7</v>
       </c>
       <c r="X7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">["TYPE"] =  7; </v>
       </c>
       <c r="Y7" t="str">
-        <f>TEXT(E7,0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z7" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AA7" t="str">
-        <f>TEXT(G7,0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AB7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="14"/>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AC7" t="str">
-        <f>TEXT(H7,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AD7" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="15"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AE7">
@@ -2813,31 +3007,7110 @@
         <v>1</v>
       </c>
       <c r="AF7" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="16"/>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AG7" t="str">
+        <f t="shared" si="17"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH7" t="str">
+        <f t="shared" si="18"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Lake-master"; }; </v>
+      </c>
+      <c r="AI7" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = "Find and catch all twenty types of eastern, freshwater fish!"; }; </v>
+      </c>
+      <c r="AJ7" t="str">
+        <f t="shared" si="20"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = "Catch all 20 fish varieties in Lake-town"; }; </v>
+      </c>
+      <c r="AK7" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["TITLE"] = { ["EN"] = "Lake-master"; }; </v>
+      </c>
+      <c r="AL7" t="str">
+        <f t="shared" si="22"/>
+        <v>};</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B1">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0167BB01-205D-43FC-93D0-141B65BF993A}">
+  <dimension ref="A1:AL66"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="0" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="0" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="0" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.140625" customWidth="1"/>
+    <col min="16" max="16" width="43.5703125" customWidth="1"/>
+    <col min="22" max="22" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" t="s">
+        <v>167</v>
+      </c>
+      <c r="N1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" t="s">
+        <v>169</v>
+      </c>
+      <c r="P1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" t="s">
+        <v>13</v>
+      </c>
+      <c r="S1" t="s">
+        <v>166</v>
+      </c>
+      <c r="T1" t="s">
+        <v>168</v>
+      </c>
+      <c r="U1" t="s">
+        <v>167</v>
+      </c>
+      <c r="V1" t="s">
+        <v>141</v>
+      </c>
+      <c r="W1" t="s">
+        <v>14</v>
+      </c>
+      <c r="X1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>164</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1879490678</v>
+      </c>
+      <c r="C2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="str">
+        <f>CONCATENATE(R2,T2,U2,AL2," -- ",C2)</f>
+        <v xml:space="preserve">  [1] = {["ID"] = 1879490678; }; -- All the Birds of Bree-land</v>
+      </c>
+      <c r="P2" s="1" t="e">
+        <f t="shared" ref="P2:P7" si="0">CONCATENATE(R2,S2,V2,X2,Z2,AB2,AD2,AF2,AG2,AH2,AI2,AJ2,AK2,AL2)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Q2">
+        <f>ROW()-1</f>
+        <v>1</v>
+      </c>
+      <c r="R2" t="str">
+        <f>CONCATENATE(REPT(" ",3-LEN(Q2)),"[",Q2,"] = {")</f>
+        <v xml:space="preserve">  [1] = {</v>
+      </c>
+      <c r="S2" t="str">
+        <f t="shared" ref="S2:S7" si="1">IF(LEN(A2)&gt;0,CONCATENATE("[""ID""] = ",A2,"; "),"                     ")</f>
+        <v xml:space="preserve">["ID"] = 1879490678; </v>
+      </c>
+      <c r="T2" t="str">
+        <f t="shared" ref="T2:T7" si="2">IF(LEN(A2)&gt;0,CONCATENATE("[""ID""] = ",A2,"; "),"")</f>
+        <v xml:space="preserve">["ID"] = 1879490678; </v>
+      </c>
+      <c r="U2" t="str">
+        <f t="shared" ref="U2:U7" si="3">IF(LEN(M2)&gt;0,CONCATENATE("[""CAT_ID""] = ",M2,"; "),"")</f>
+        <v/>
+      </c>
+      <c r="V2" s="1" t="str">
+        <f t="shared" ref="V2:V7" si="4">IF(LEN(B2)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B2)),B2,"; "),"")</f>
+        <v/>
+      </c>
+      <c r="W2" t="e">
+        <f>VLOOKUP(D2,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X2" t="e">
+        <f>CONCATENATE("[""TYPE""] = ",REPT(" ",2-LEN(W2)),W2,"; ")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Y2" t="str">
+        <f t="shared" ref="Y2:Y7" si="5">TEXT(E2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z2" t="str">
+        <f>CONCATENATE("[""VXP""] = ",REPT(" ",1-LEN(Y2)),TEXT(Y2,"0"),"; ")</f>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA2" t="str">
+        <f t="shared" ref="AA2:AA7" si="6">TEXT(G2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AB2" t="str">
+        <f>CONCATENATE("[""LP""] = ",REPT(" ",1-LEN(AA2)),TEXT(AA2,"0"),"; ")</f>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC2" t="str">
+        <f t="shared" ref="AC2:AC7" si="7">TEXT(H2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD2" t="str">
+        <f>CONCATENATE("[""REP""] = ",REPT(" ",1-LEN(AC2)),TEXT(AC2,"0"),"; ")</f>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE2">
+        <f>VLOOKUP(I2,Faction!A$2:B$77,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="str">
+        <f t="shared" ref="AF2:AF7" si="8">CONCATENATE("[""FACTION""] = ",TEXT(AE2,"0"),"; ")</f>
+        <v xml:space="preserve">["FACTION"] = 1; </v>
+      </c>
+      <c r="AG2" t="str">
+        <f>CONCATENATE("[""TIER""] = ",TEXT(L2,"0"),"; ")</f>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH2" t="str">
+        <f>CONCATENATE("[""NAME""] = { [""EN""] = """,C2,"""; }; ")</f>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Bree-land"; }; </v>
+      </c>
+      <c r="AI2" t="str">
+        <f>CONCATENATE("[""LORE""] = { [""EN""] = """,K2,"""; }; ")</f>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ2" t="str">
+        <f>CONCATENATE("[""SUMMARY""] = { [""EN""] = """,J2,"""; }; ")</f>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK2" t="str">
+        <f>IF(LEN(F2)&gt;0,CONCATENATE("[""TITLE""] = { [""EN""] = """,F2,"""; }; "),"")</f>
+        <v/>
+      </c>
+      <c r="AL2" t="str">
+        <f>CONCATENATE("};")</f>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1879490611</v>
+      </c>
+      <c r="C3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I3" t="s">
+        <v>79</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="O3" t="str">
+        <f t="shared" ref="O3:O66" si="9">CONCATENATE(R3,T3,U3,AL3," -- ",C3)</f>
+        <v xml:space="preserve">  [2] = {["ID"] = 1879490611; }; -- Birds of Bree-land: Common and Uncommon</v>
+      </c>
+      <c r="P3" s="1" t="e">
+        <f t="shared" ref="P3:P66" si="10">CONCATENATE(R3,S3,V3,X3,Z3,AB3,AD3,AF3,AG3,AH3,AI3,AJ3,AK3,AL3)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q66" si="11">ROW()-1</f>
+        <v>2</v>
+      </c>
+      <c r="R3" t="str">
+        <f t="shared" ref="R3:R66" si="12">CONCATENATE(REPT(" ",3-LEN(Q3)),"[",Q3,"] = {")</f>
+        <v xml:space="preserve">  [2] = {</v>
+      </c>
+      <c r="S3" t="str">
+        <f t="shared" ref="S3:S66" si="13">IF(LEN(A3)&gt;0,CONCATENATE("[""ID""] = ",A3,"; "),"                     ")</f>
+        <v xml:space="preserve">["ID"] = 1879490611; </v>
+      </c>
+      <c r="T3" t="str">
+        <f t="shared" ref="T3:T66" si="14">IF(LEN(A3)&gt;0,CONCATENATE("[""ID""] = ",A3,"; "),"")</f>
+        <v xml:space="preserve">["ID"] = 1879490611; </v>
+      </c>
+      <c r="U3" t="str">
+        <f t="shared" ref="U3:U66" si="15">IF(LEN(M3)&gt;0,CONCATENATE("[""CAT_ID""] = ",M3,"; "),"")</f>
+        <v/>
+      </c>
+      <c r="V3" s="1" t="str">
+        <f t="shared" ref="V3:V66" si="16">IF(LEN(B3)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B3)),B3,"; "),"")</f>
+        <v/>
+      </c>
+      <c r="W3" t="e">
+        <f>VLOOKUP(D3,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X3" t="e">
+        <f t="shared" ref="X3:X66" si="17">CONCATENATE("[""TYPE""] = ",REPT(" ",2-LEN(W3)),W3,"; ")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Y3" t="str">
+        <f t="shared" ref="Y3:Y66" si="18">TEXT(E3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z3" t="str">
+        <f t="shared" ref="Z3:Z66" si="19">CONCATENATE("[""VXP""] = ",REPT(" ",1-LEN(Y3)),TEXT(Y3,"0"),"; ")</f>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA3" t="str">
+        <f t="shared" ref="AA3:AA66" si="20">TEXT(G3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AB3" t="str">
+        <f t="shared" ref="AB3:AB66" si="21">CONCATENATE("[""LP""] = ",REPT(" ",1-LEN(AA3)),TEXT(AA3,"0"),"; ")</f>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC3" t="str">
+        <f t="shared" ref="AC3:AC66" si="22">TEXT(H3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD3" t="str">
+        <f t="shared" ref="AD3:AD66" si="23">CONCATENATE("[""REP""] = ",REPT(" ",1-LEN(AC3)),TEXT(AC3,"0"),"; ")</f>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE3">
+        <f>VLOOKUP(I3,Faction!A$2:B$77,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="AF3" t="str">
+        <f t="shared" ref="AF3:AF66" si="24">CONCATENATE("[""FACTION""] = ",TEXT(AE3,"0"),"; ")</f>
+        <v xml:space="preserve">["FACTION"] = 1; </v>
+      </c>
+      <c r="AG3" t="str">
+        <f t="shared" ref="AG3:AG66" si="25">CONCATENATE("[""TIER""] = ",TEXT(L3,"0"),"; ")</f>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH3" t="str">
+        <f t="shared" ref="AH3:AH66" si="26">CONCATENATE("[""NAME""] = { [""EN""] = """,C3,"""; }; ")</f>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Bree-land: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AI3" t="str">
+        <f t="shared" ref="AI3:AI66" si="27">CONCATENATE("[""LORE""] = { [""EN""] = """,K3,"""; }; ")</f>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ3" t="str">
+        <f t="shared" ref="AJ3:AJ66" si="28">CONCATENATE("[""SUMMARY""] = { [""EN""] = """,J3,"""; }; ")</f>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK3" t="str">
+        <f t="shared" ref="AK3:AK66" si="29">IF(LEN(F3)&gt;0,CONCATENATE("[""TITLE""] = { [""EN""] = """,F3,"""; }; "),"")</f>
+        <v/>
+      </c>
+      <c r="AL3" t="str">
+        <f t="shared" ref="AL3:AL66" si="30">CONCATENATE("};")</f>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1879490469</v>
+      </c>
+      <c r="C4" t="s">
+        <v>172</v>
+      </c>
+      <c r="I4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="O4" t="str">
         <f t="shared" si="9"/>
+        <v xml:space="preserve">  [3] = {["ID"] = 1879490469; }; -- Birds of Bree-land: Rare</v>
+      </c>
+      <c r="P4" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="R4" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">  [3] = {</v>
+      </c>
+      <c r="S4" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490469; </v>
+      </c>
+      <c r="T4" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490469; </v>
+      </c>
+      <c r="U4" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V4" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W4" t="e">
+        <f>VLOOKUP(D4,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X4" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y4" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z4" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA4" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB4" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC4" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD4" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE4">
+        <f>VLOOKUP(I4,Faction!A$2:B$77,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="AF4" t="str">
+        <f t="shared" si="24"/>
+        <v xml:space="preserve">["FACTION"] = 1; </v>
+      </c>
+      <c r="AG4" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 2; </v>
+      </c>
+      <c r="AH4" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Bree-land: Rare"; }; </v>
+      </c>
+      <c r="AI4" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ4" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK4" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL4" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1879490610</v>
+      </c>
+      <c r="C5" t="s">
+        <v>173</v>
+      </c>
+      <c r="I5" t="s">
+        <v>79</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="O5" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">  [4] = {["ID"] = 1879490610; }; -- The Rarest Bird in Bree-land</v>
+      </c>
+      <c r="P5" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+      <c r="R5" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">  [4] = {</v>
+      </c>
+      <c r="S5" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490610; </v>
+      </c>
+      <c r="T5" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490610; </v>
+      </c>
+      <c r="U5" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V5" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W5" t="e">
+        <f>VLOOKUP(D5,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X5" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y5" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z5" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA5" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB5" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC5" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD5" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE5">
+        <f>VLOOKUP(I5,Faction!A$2:B$77,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="AF5" t="str">
+        <f t="shared" si="24"/>
+        <v xml:space="preserve">["FACTION"] = 1; </v>
+      </c>
+      <c r="AG5" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 3; </v>
+      </c>
+      <c r="AH5" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Bree-land"; }; </v>
+      </c>
+      <c r="AI5" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ5" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK5" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL5" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1879490682</v>
+      </c>
+      <c r="C6" t="s">
+        <v>174</v>
+      </c>
+      <c r="I6" t="s">
+        <v>79</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">  [5] = {["ID"] = 1879490682; }; -- All the Birds of the Shire</v>
+      </c>
+      <c r="P6" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+      <c r="R6" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">  [5] = {</v>
+      </c>
+      <c r="S6" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490682; </v>
+      </c>
+      <c r="T6" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490682; </v>
+      </c>
+      <c r="U6" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V6" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W6" t="e">
+        <f>VLOOKUP(D6,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X6" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y6" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z6" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA6" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB6" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC6" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD6" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE6">
+        <f>VLOOKUP(I6,Faction!A$2:B$77,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="AF6" t="str">
+        <f t="shared" si="24"/>
+        <v xml:space="preserve">["FACTION"] = 1; </v>
+      </c>
+      <c r="AG6" t="str">
+        <f t="shared" si="25"/>
         <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
+      <c r="AH6" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of the Shire"; }; </v>
+      </c>
+      <c r="AI6" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ6" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK6" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL6" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1879490617</v>
+      </c>
+      <c r="C7" t="s">
+        <v>177</v>
+      </c>
+      <c r="I7" t="s">
+        <v>79</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="O7" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">  [6] = {["ID"] = 1879490617; }; -- Birds of The Shire: Common and Uncommon</v>
+      </c>
+      <c r="P7" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="11"/>
+        <v>6</v>
+      </c>
+      <c r="R7" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">  [6] = {</v>
+      </c>
+      <c r="S7" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490617; </v>
+      </c>
+      <c r="T7" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490617; </v>
+      </c>
+      <c r="U7" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V7" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W7" t="e">
+        <f>VLOOKUP(D7,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X7" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y7" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z7" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA7" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB7" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC7" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD7" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE7">
+        <f>VLOOKUP(I7,Faction!A$2:B$77,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="AF7" t="str">
+        <f t="shared" si="24"/>
+        <v xml:space="preserve">["FACTION"] = 1; </v>
+      </c>
+      <c r="AG7" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
       <c r="AH7" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of The Shire: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AI7" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ7" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK7" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL7" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1879490640</v>
+      </c>
+      <c r="C8" t="s">
+        <v>176</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="O8" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">  [7] = {["ID"] = 1879490640; }; -- Birds of The Shire: Rare</v>
+      </c>
+      <c r="P8" s="1" t="e">
         <f t="shared" si="10"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Lake-master"; }; </v>
-      </c>
-      <c r="AI7" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="Q8">
         <f t="shared" si="11"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = "Find and catch all twenty types of eastern, freshwater fish!"; }; </v>
-      </c>
-      <c r="AJ7" t="str">
+        <v>7</v>
+      </c>
+      <c r="R8" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = "Catch all 20 fish varieties in Lake-town"; }; </v>
-      </c>
-      <c r="AK7" t="str">
+        <v xml:space="preserve">  [7] = {</v>
+      </c>
+      <c r="S8" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["TITLE"] = { ["EN"] = "Lake-master"; }; </v>
-      </c>
-      <c r="AL7" t="str">
+        <v xml:space="preserve">["ID"] = 1879490640; </v>
+      </c>
+      <c r="T8" t="str">
         <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490640; </v>
+      </c>
+      <c r="U8" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V8" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W8" t="e">
+        <f>VLOOKUP(D8,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X8" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y8" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z8" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA8" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB8" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC8" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD8" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE8" t="e">
+        <f>VLOOKUP(I8,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF8" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG8" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 2; </v>
+      </c>
+      <c r="AH8" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of The Shire: Rare"; }; </v>
+      </c>
+      <c r="AI8" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ8" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK8" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL8" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1879490622</v>
+      </c>
+      <c r="C9" t="s">
+        <v>175</v>
+      </c>
+      <c r="L9">
+        <v>3</v>
+      </c>
+      <c r="O9" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">  [8] = {["ID"] = 1879490622; }; -- The Rarest Bird in The Shire</v>
+      </c>
+      <c r="P9" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="11"/>
+        <v>8</v>
+      </c>
+      <c r="R9" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">  [8] = {</v>
+      </c>
+      <c r="S9" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490622; </v>
+      </c>
+      <c r="T9" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490622; </v>
+      </c>
+      <c r="U9" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V9" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W9" t="e">
+        <f>VLOOKUP(D9,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X9" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y9" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z9" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA9" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB9" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC9" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD9" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE9" t="e">
+        <f>VLOOKUP(I9,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF9" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG9" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 3; </v>
+      </c>
+      <c r="AH9" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in The Shire"; }; </v>
+      </c>
+      <c r="AI9" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ9" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK9" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL9" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1879490671</v>
+      </c>
+      <c r="C10" t="s">
+        <v>178</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="O10" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">  [9] = {["ID"] = 1879490671; }; -- All the Birds of Ered Luin</v>
+      </c>
+      <c r="P10" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="11"/>
+        <v>9</v>
+      </c>
+      <c r="R10" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve">  [9] = {</v>
+      </c>
+      <c r="S10" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490671; </v>
+      </c>
+      <c r="T10" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490671; </v>
+      </c>
+      <c r="U10" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V10" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W10" t="e">
+        <f>VLOOKUP(D10,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X10" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y10" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z10" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA10" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB10" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC10" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD10" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE10" t="e">
+        <f>VLOOKUP(I10,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF10" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG10" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH10" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Ered Luin"; }; </v>
+      </c>
+      <c r="AI10" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ10" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK10" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL10" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1879490651</v>
+      </c>
+      <c r="C11" t="s">
+        <v>181</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="O11" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [10] = {["ID"] = 1879490651; }; -- Birds of Ered Luin: Common and Uncommon</v>
+      </c>
+      <c r="P11" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="11"/>
+        <v>10</v>
+      </c>
+      <c r="R11" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [10] = {</v>
+      </c>
+      <c r="S11" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490651; </v>
+      </c>
+      <c r="T11" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490651; </v>
+      </c>
+      <c r="U11" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V11" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W11" t="e">
+        <f>VLOOKUP(D11,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X11" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y11" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z11" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA11" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB11" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC11" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD11" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE11" t="e">
+        <f>VLOOKUP(I11,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF11" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG11" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH11" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Ered Luin: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AI11" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ11" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK11" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL11" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1879490635</v>
+      </c>
+      <c r="C12" t="s">
+        <v>180</v>
+      </c>
+      <c r="L12">
+        <v>2</v>
+      </c>
+      <c r="O12" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [11] = {["ID"] = 1879490635; }; -- Birds of Ered Luin: Rare</v>
+      </c>
+      <c r="P12" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="11"/>
+        <v>11</v>
+      </c>
+      <c r="R12" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [11] = {</v>
+      </c>
+      <c r="S12" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490635; </v>
+      </c>
+      <c r="T12" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490635; </v>
+      </c>
+      <c r="U12" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V12" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W12" t="e">
+        <f>VLOOKUP(D12,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X12" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y12" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z12" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA12" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB12" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC12" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD12" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE12" t="e">
+        <f>VLOOKUP(I12,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF12" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG12" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 2; </v>
+      </c>
+      <c r="AH12" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Ered Luin: Rare"; }; </v>
+      </c>
+      <c r="AI12" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ12" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK12" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL12" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1879490633</v>
+      </c>
+      <c r="C13" t="s">
+        <v>179</v>
+      </c>
+      <c r="L13">
+        <v>3</v>
+      </c>
+      <c r="O13" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [12] = {["ID"] = 1879490633; }; -- The Rarest Bird in Ered Luin</v>
+      </c>
+      <c r="P13" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="11"/>
+        <v>12</v>
+      </c>
+      <c r="R13" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [12] = {</v>
+      </c>
+      <c r="S13" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490633; </v>
+      </c>
+      <c r="T13" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490633; </v>
+      </c>
+      <c r="U13" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V13" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W13" t="e">
+        <f>VLOOKUP(D13,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X13" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y13" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z13" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA13" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB13" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC13" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD13" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE13" t="e">
+        <f>VLOOKUP(I13,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF13" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG13" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 3; </v>
+      </c>
+      <c r="AH13" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Ered Luin"; }; </v>
+      </c>
+      <c r="AI13" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ13" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK13" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL13" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1879490668</v>
+      </c>
+      <c r="C14" t="s">
+        <v>182</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="O14" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [13] = {["ID"] = 1879490668; }; -- All the Birds of Swanfleet</v>
+      </c>
+      <c r="P14" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="11"/>
+        <v>13</v>
+      </c>
+      <c r="R14" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [13] = {</v>
+      </c>
+      <c r="S14" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490668; </v>
+      </c>
+      <c r="T14" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490668; </v>
+      </c>
+      <c r="U14" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V14" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W14" t="e">
+        <f>VLOOKUP(D14,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X14" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y14" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z14" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA14" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB14" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC14" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD14" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE14" t="e">
+        <f>VLOOKUP(I14,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF14" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG14" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH14" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Swanfleet"; }; </v>
+      </c>
+      <c r="AI14" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ14" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK14" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL14" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1879490642</v>
+      </c>
+      <c r="C15" t="s">
+        <v>183</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="O15" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [14] = {["ID"] = 1879490642; }; -- Birds of Swanfleet: Common and Uncommon</v>
+      </c>
+      <c r="P15" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="11"/>
+        <v>14</v>
+      </c>
+      <c r="R15" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [14] = {</v>
+      </c>
+      <c r="S15" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490642; </v>
+      </c>
+      <c r="T15" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490642; </v>
+      </c>
+      <c r="U15" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V15" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W15" t="e">
+        <f>VLOOKUP(D15,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X15" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y15" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z15" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA15" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB15" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC15" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD15" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE15" t="e">
+        <f>VLOOKUP(I15,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF15" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG15" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH15" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Swanfleet: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AI15" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ15" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK15" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL15" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1879490641</v>
+      </c>
+      <c r="C16" t="s">
+        <v>184</v>
+      </c>
+      <c r="L16">
+        <v>2</v>
+      </c>
+      <c r="O16" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [15] = {["ID"] = 1879490641; }; -- Birds of Swanfleet: Rare</v>
+      </c>
+      <c r="P16" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="11"/>
+        <v>15</v>
+      </c>
+      <c r="R16" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [15] = {</v>
+      </c>
+      <c r="S16" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490641; </v>
+      </c>
+      <c r="T16" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490641; </v>
+      </c>
+      <c r="U16" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V16" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W16" t="e">
+        <f>VLOOKUP(D16,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X16" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y16" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z16" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA16" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB16" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC16" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD16" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE16" t="e">
+        <f>VLOOKUP(I16,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF16" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG16" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 2; </v>
+      </c>
+      <c r="AH16" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Swanfleet: Rare"; }; </v>
+      </c>
+      <c r="AI16" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ16" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK16" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL16" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>1879490645</v>
+      </c>
+      <c r="C17" t="s">
+        <v>185</v>
+      </c>
+      <c r="L17">
+        <v>3</v>
+      </c>
+      <c r="O17" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [16] = {["ID"] = 1879490645; }; -- The Rarest Bird in Swanfleet</v>
+      </c>
+      <c r="P17" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="11"/>
+        <v>16</v>
+      </c>
+      <c r="R17" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [16] = {</v>
+      </c>
+      <c r="S17" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490645; </v>
+      </c>
+      <c r="T17" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490645; </v>
+      </c>
+      <c r="U17" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V17" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W17" t="e">
+        <f>VLOOKUP(D17,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X17" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y17" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z17" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA17" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB17" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC17" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD17" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE17" t="e">
+        <f>VLOOKUP(I17,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF17" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG17" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 3; </v>
+      </c>
+      <c r="AH17" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Swanfleet"; }; </v>
+      </c>
+      <c r="AI17" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ17" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK17" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL17" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>1879490670</v>
+      </c>
+      <c r="C18" t="s">
+        <v>226</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="O18" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [17] = {["ID"] = 1879490670; }; -- All the Birds of Cardolan</v>
+      </c>
+      <c r="P18" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="11"/>
+        <v>17</v>
+      </c>
+      <c r="R18" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [17] = {</v>
+      </c>
+      <c r="S18" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490670; </v>
+      </c>
+      <c r="T18" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490670; </v>
+      </c>
+      <c r="U18" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V18" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W18" t="e">
+        <f>VLOOKUP(D18,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X18" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y18" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z18" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA18" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB18" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC18" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD18" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE18" t="e">
+        <f>VLOOKUP(I18,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF18" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG18" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH18" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Cardolan"; }; </v>
+      </c>
+      <c r="AI18" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ18" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK18" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL18" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1879490621</v>
+      </c>
+      <c r="C19" t="s">
+        <v>227</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="O19" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [18] = {["ID"] = 1879490621; }; -- Birds of Cardolan: Common and Uncommon</v>
+      </c>
+      <c r="P19" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="11"/>
+        <v>18</v>
+      </c>
+      <c r="R19" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [18] = {</v>
+      </c>
+      <c r="S19" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490621; </v>
+      </c>
+      <c r="T19" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490621; </v>
+      </c>
+      <c r="U19" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V19" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W19" t="e">
+        <f>VLOOKUP(D19,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X19" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y19" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z19" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA19" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB19" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC19" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD19" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE19" t="e">
+        <f>VLOOKUP(I19,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF19" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG19" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH19" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Cardolan: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AI19" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ19" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK19" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL19" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>1879490627</v>
+      </c>
+      <c r="C20" t="s">
+        <v>228</v>
+      </c>
+      <c r="L20">
+        <v>2</v>
+      </c>
+      <c r="O20" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [19] = {["ID"] = 1879490627; }; -- Birds of Cardolan: Rare</v>
+      </c>
+      <c r="P20" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="11"/>
+        <v>19</v>
+      </c>
+      <c r="R20" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [19] = {</v>
+      </c>
+      <c r="S20" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490627; </v>
+      </c>
+      <c r="T20" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490627; </v>
+      </c>
+      <c r="U20" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V20" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W20" t="e">
+        <f>VLOOKUP(D20,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X20" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y20" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z20" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA20" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB20" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC20" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD20" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE20" t="e">
+        <f>VLOOKUP(I20,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF20" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG20" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 2; </v>
+      </c>
+      <c r="AH20" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Cardolan: Rare"; }; </v>
+      </c>
+      <c r="AI20" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ20" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK20" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL20" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>1879490647</v>
+      </c>
+      <c r="C21" t="s">
+        <v>229</v>
+      </c>
+      <c r="L21">
+        <v>3</v>
+      </c>
+      <c r="O21" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [20] = {["ID"] = 1879490647; }; -- The Rarest Bird in Cardolan</v>
+      </c>
+      <c r="P21" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="11"/>
+        <v>20</v>
+      </c>
+      <c r="R21" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [20] = {</v>
+      </c>
+      <c r="S21" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490647; </v>
+      </c>
+      <c r="T21" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490647; </v>
+      </c>
+      <c r="U21" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V21" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W21" t="e">
+        <f>VLOOKUP(D21,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X21" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y21" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z21" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA21" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB21" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC21" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD21" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE21" t="e">
+        <f>VLOOKUP(I21,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF21" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG21" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 3; </v>
+      </c>
+      <c r="AH21" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Cardolan"; }; </v>
+      </c>
+      <c r="AI21" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ21" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK21" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL21" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>1879490676</v>
+      </c>
+      <c r="C22" t="s">
+        <v>186</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="O22" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [21] = {["ID"] = 1879490676; }; -- All the Birds of the Lone-lands</v>
+      </c>
+      <c r="P22" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="11"/>
+        <v>21</v>
+      </c>
+      <c r="R22" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [21] = {</v>
+      </c>
+      <c r="S22" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490676; </v>
+      </c>
+      <c r="T22" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490676; </v>
+      </c>
+      <c r="U22" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V22" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W22" t="e">
+        <f>VLOOKUP(D22,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X22" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y22" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z22" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA22" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB22" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC22" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD22" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE22" t="e">
+        <f>VLOOKUP(I22,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF22" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG22" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH22" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of the Lone-lands"; }; </v>
+      </c>
+      <c r="AI22" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ22" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK22" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL22" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>1879490649</v>
+      </c>
+      <c r="C23" t="s">
+        <v>187</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="O23" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [22] = {["ID"] = 1879490649; }; -- Birds of the Lone-lands: Common and Uncommon</v>
+      </c>
+      <c r="P23" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="11"/>
+        <v>22</v>
+      </c>
+      <c r="R23" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [22] = {</v>
+      </c>
+      <c r="S23" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490649; </v>
+      </c>
+      <c r="T23" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490649; </v>
+      </c>
+      <c r="U23" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V23" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W23" t="e">
+        <f>VLOOKUP(D23,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X23" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y23" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z23" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA23" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB23" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC23" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD23" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE23" t="e">
+        <f>VLOOKUP(I23,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF23" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG23" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH23" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Lone-lands: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AI23" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ23" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK23" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL23" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>1879490632</v>
+      </c>
+      <c r="C24" t="s">
+        <v>188</v>
+      </c>
+      <c r="L24">
+        <v>2</v>
+      </c>
+      <c r="O24" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [23] = {["ID"] = 1879490632; }; -- Birds of the Lone-lands: Rare</v>
+      </c>
+      <c r="P24" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="11"/>
+        <v>23</v>
+      </c>
+      <c r="R24" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [23] = {</v>
+      </c>
+      <c r="S24" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490632; </v>
+      </c>
+      <c r="T24" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490632; </v>
+      </c>
+      <c r="U24" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V24" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W24" t="e">
+        <f>VLOOKUP(D24,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X24" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y24" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z24" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA24" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB24" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC24" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD24" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE24" t="e">
+        <f>VLOOKUP(I24,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF24" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG24" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 2; </v>
+      </c>
+      <c r="AH24" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Lone-lands: Rare"; }; </v>
+      </c>
+      <c r="AI24" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ24" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK24" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL24" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>1879490637</v>
+      </c>
+      <c r="C25" t="s">
+        <v>189</v>
+      </c>
+      <c r="L25">
+        <v>3</v>
+      </c>
+      <c r="O25" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [24] = {["ID"] = 1879490637; }; -- The Rarest Bird in the Lone-lands</v>
+      </c>
+      <c r="P25" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="11"/>
+        <v>24</v>
+      </c>
+      <c r="R25" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [24] = {</v>
+      </c>
+      <c r="S25" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490637; </v>
+      </c>
+      <c r="T25" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490637; </v>
+      </c>
+      <c r="U25" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V25" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W25" t="e">
+        <f>VLOOKUP(D25,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X25" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y25" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z25" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA25" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB25" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC25" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD25" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE25" t="e">
+        <f>VLOOKUP(I25,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF25" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG25" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 3; </v>
+      </c>
+      <c r="AH25" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in the Lone-lands"; }; </v>
+      </c>
+      <c r="AI25" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ25" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK25" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL25" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>1879490675</v>
+      </c>
+      <c r="C26" t="s">
+        <v>190</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="O26" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [25] = {["ID"] = 1879490675; }; -- All the Birds of the North Downs</v>
+      </c>
+      <c r="P26" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="11"/>
+        <v>25</v>
+      </c>
+      <c r="R26" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [25] = {</v>
+      </c>
+      <c r="S26" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490675; </v>
+      </c>
+      <c r="T26" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490675; </v>
+      </c>
+      <c r="U26" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V26" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W26" t="e">
+        <f>VLOOKUP(D26,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X26" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y26" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z26" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA26" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB26" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC26" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD26" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE26" t="e">
+        <f>VLOOKUP(I26,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF26" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG26" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH26" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of the North Downs"; }; </v>
+      </c>
+      <c r="AI26" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ26" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK26" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL26" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>1879490630</v>
+      </c>
+      <c r="C27" t="s">
+        <v>191</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="O27" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [26] = {["ID"] = 1879490630; }; -- Birds of The North Downs: Common and Uncommon</v>
+      </c>
+      <c r="P27" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q27">
+        <f t="shared" si="11"/>
+        <v>26</v>
+      </c>
+      <c r="R27" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [26] = {</v>
+      </c>
+      <c r="S27" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490630; </v>
+      </c>
+      <c r="T27" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490630; </v>
+      </c>
+      <c r="U27" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V27" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W27" t="e">
+        <f>VLOOKUP(D27,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X27" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y27" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z27" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA27" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB27" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC27" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD27" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE27" t="e">
+        <f>VLOOKUP(I27,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF27" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG27" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH27" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of The North Downs: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AI27" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ27" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK27" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL27" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>1879490626</v>
+      </c>
+      <c r="C28" t="s">
+        <v>192</v>
+      </c>
+      <c r="L28">
+        <v>2</v>
+      </c>
+      <c r="O28" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [27] = {["ID"] = 1879490626; }; -- Birds of the North Downs: Rare</v>
+      </c>
+      <c r="P28" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q28">
+        <f t="shared" si="11"/>
+        <v>27</v>
+      </c>
+      <c r="R28" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [27] = {</v>
+      </c>
+      <c r="S28" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490626; </v>
+      </c>
+      <c r="T28" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490626; </v>
+      </c>
+      <c r="U28" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V28" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W28" t="e">
+        <f>VLOOKUP(D28,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X28" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y28" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z28" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA28" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB28" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC28" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD28" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE28" t="e">
+        <f>VLOOKUP(I28,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF28" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG28" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 2; </v>
+      </c>
+      <c r="AH28" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the North Downs: Rare"; }; </v>
+      </c>
+      <c r="AI28" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ28" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK28" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL28" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>1879490625</v>
+      </c>
+      <c r="C29" t="s">
+        <v>193</v>
+      </c>
+      <c r="L29">
+        <v>3</v>
+      </c>
+      <c r="O29" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [28] = {["ID"] = 1879490625; }; -- The Rarest Bird in the North Downs</v>
+      </c>
+      <c r="P29" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q29">
+        <f t="shared" si="11"/>
+        <v>28</v>
+      </c>
+      <c r="R29" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [28] = {</v>
+      </c>
+      <c r="S29" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490625; </v>
+      </c>
+      <c r="T29" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490625; </v>
+      </c>
+      <c r="U29" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V29" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W29" t="e">
+        <f>VLOOKUP(D29,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X29" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y29" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z29" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA29" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB29" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC29" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD29" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE29" t="e">
+        <f>VLOOKUP(I29,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF29" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG29" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 3; </v>
+      </c>
+      <c r="AH29" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in the North Downs"; }; </v>
+      </c>
+      <c r="AI29" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ29" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK29" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL29" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>1879490677</v>
+      </c>
+      <c r="C30" t="s">
+        <v>194</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="O30" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [29] = {["ID"] = 1879490677; }; -- All the Birds of the Trollshaws</v>
+      </c>
+      <c r="P30" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q30">
+        <f t="shared" si="11"/>
+        <v>29</v>
+      </c>
+      <c r="R30" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [29] = {</v>
+      </c>
+      <c r="S30" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490677; </v>
+      </c>
+      <c r="T30" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490677; </v>
+      </c>
+      <c r="U30" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V30" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W30" t="e">
+        <f>VLOOKUP(D30,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X30" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y30" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z30" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA30" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB30" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC30" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD30" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE30" t="e">
+        <f>VLOOKUP(I30,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF30" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG30" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH30" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of the Trollshaws"; }; </v>
+      </c>
+      <c r="AI30" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ30" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK30" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL30" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>1879490614</v>
+      </c>
+      <c r="C31" t="s">
+        <v>195</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
+      </c>
+      <c r="O31" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [30] = {["ID"] = 1879490614; }; -- Birds of the Trollshaws: Common and Uncommon</v>
+      </c>
+      <c r="P31" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q31">
+        <f t="shared" si="11"/>
+        <v>30</v>
+      </c>
+      <c r="R31" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [30] = {</v>
+      </c>
+      <c r="S31" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490614; </v>
+      </c>
+      <c r="T31" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490614; </v>
+      </c>
+      <c r="U31" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V31" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W31" t="e">
+        <f>VLOOKUP(D31,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X31" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y31" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z31" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA31" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB31" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC31" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD31" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE31" t="e">
+        <f>VLOOKUP(I31,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF31" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG31" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH31" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Trollshaws: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AI31" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ31" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK31" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL31" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>1879490639</v>
+      </c>
+      <c r="C32" t="s">
+        <v>196</v>
+      </c>
+      <c r="L32">
+        <v>2</v>
+      </c>
+      <c r="O32" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [31] = {["ID"] = 1879490639; }; -- Birds of the Trollshaws: Rare</v>
+      </c>
+      <c r="P32" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q32">
+        <f t="shared" si="11"/>
+        <v>31</v>
+      </c>
+      <c r="R32" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [31] = {</v>
+      </c>
+      <c r="S32" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490639; </v>
+      </c>
+      <c r="T32" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490639; </v>
+      </c>
+      <c r="U32" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V32" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W32" t="e">
+        <f>VLOOKUP(D32,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X32" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y32" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z32" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA32" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB32" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC32" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD32" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE32" t="e">
+        <f>VLOOKUP(I32,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF32" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG32" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 2; </v>
+      </c>
+      <c r="AH32" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Trollshaws: Rare"; }; </v>
+      </c>
+      <c r="AI32" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ32" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK32" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL32" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>1879490629</v>
+      </c>
+      <c r="C33" t="s">
+        <v>197</v>
+      </c>
+      <c r="L33">
+        <v>3</v>
+      </c>
+      <c r="O33" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [32] = {["ID"] = 1879490629; }; -- The Rarest Bird in the Trollshaws</v>
+      </c>
+      <c r="P33" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q33">
+        <f t="shared" si="11"/>
+        <v>32</v>
+      </c>
+      <c r="R33" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [32] = {</v>
+      </c>
+      <c r="S33" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490629; </v>
+      </c>
+      <c r="T33" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490629; </v>
+      </c>
+      <c r="U33" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V33" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W33" t="e">
+        <f>VLOOKUP(D33,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X33" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y33" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z33" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA33" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB33" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC33" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD33" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE33" t="e">
+        <f>VLOOKUP(I33,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF33" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG33" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 3; </v>
+      </c>
+      <c r="AH33" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in the Trollshaws"; }; </v>
+      </c>
+      <c r="AI33" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ33" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK33" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL33" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>1879490673</v>
+      </c>
+      <c r="C34" t="s">
+        <v>198</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="O34" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [33] = {["ID"] = 1879490673; }; -- All the Birds of the Misty Mountains</v>
+      </c>
+      <c r="P34" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q34">
+        <f t="shared" si="11"/>
+        <v>33</v>
+      </c>
+      <c r="R34" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [33] = {</v>
+      </c>
+      <c r="S34" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490673; </v>
+      </c>
+      <c r="T34" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490673; </v>
+      </c>
+      <c r="U34" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V34" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W34" t="e">
+        <f>VLOOKUP(D34,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X34" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y34" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z34" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA34" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB34" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC34" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD34" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE34" t="e">
+        <f>VLOOKUP(I34,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF34" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG34" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH34" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of the Misty Mountains"; }; </v>
+      </c>
+      <c r="AI34" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ34" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK34" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL34" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>1879490650</v>
+      </c>
+      <c r="C35" t="s">
+        <v>199</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+      <c r="O35" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [34] = {["ID"] = 1879490650; }; -- Birds of the Misty Mountains: Common and Uncommon</v>
+      </c>
+      <c r="P35" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q35">
+        <f t="shared" si="11"/>
+        <v>34</v>
+      </c>
+      <c r="R35" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [34] = {</v>
+      </c>
+      <c r="S35" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490650; </v>
+      </c>
+      <c r="T35" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490650; </v>
+      </c>
+      <c r="U35" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V35" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W35" t="e">
+        <f>VLOOKUP(D35,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X35" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y35" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z35" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA35" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB35" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC35" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD35" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE35" t="e">
+        <f>VLOOKUP(I35,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF35" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG35" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH35" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Misty Mountains: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AI35" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ35" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK35" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL35" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>1879490620</v>
+      </c>
+      <c r="C36" t="s">
+        <v>200</v>
+      </c>
+      <c r="L36">
+        <v>2</v>
+      </c>
+      <c r="O36" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [35] = {["ID"] = 1879490620; }; -- Birds of the Misty Mountains: Rare</v>
+      </c>
+      <c r="P36" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q36">
+        <f t="shared" si="11"/>
+        <v>35</v>
+      </c>
+      <c r="R36" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [35] = {</v>
+      </c>
+      <c r="S36" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490620; </v>
+      </c>
+      <c r="T36" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490620; </v>
+      </c>
+      <c r="U36" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V36" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W36" t="e">
+        <f>VLOOKUP(D36,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X36" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y36" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z36" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA36" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB36" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC36" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD36" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE36" t="e">
+        <f>VLOOKUP(I36,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF36" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG36" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 2; </v>
+      </c>
+      <c r="AH36" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Misty Mountains: Rare"; }; </v>
+      </c>
+      <c r="AI36" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ36" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK36" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL36" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>1879490612</v>
+      </c>
+      <c r="C37" t="s">
+        <v>201</v>
+      </c>
+      <c r="L37">
+        <v>3</v>
+      </c>
+      <c r="O37" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [36] = {["ID"] = 1879490612; }; -- The Rarest Bird in the Misty Mountains</v>
+      </c>
+      <c r="P37" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q37">
+        <f t="shared" si="11"/>
+        <v>36</v>
+      </c>
+      <c r="R37" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [36] = {</v>
+      </c>
+      <c r="S37" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490612; </v>
+      </c>
+      <c r="T37" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490612; </v>
+      </c>
+      <c r="U37" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V37" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W37" t="e">
+        <f>VLOOKUP(D37,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X37" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y37" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z37" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA37" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB37" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC37" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD37" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE37" t="e">
+        <f>VLOOKUP(I37,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF37" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG37" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 3; </v>
+      </c>
+      <c r="AH37" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in the Misty Mountains"; }; </v>
+      </c>
+      <c r="AI37" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ37" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK37" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL37" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>1879490674</v>
+      </c>
+      <c r="C38" t="s">
+        <v>202</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="O38" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [37] = {["ID"] = 1879490674; }; -- All the Birds of Evendim</v>
+      </c>
+      <c r="P38" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q38">
+        <f t="shared" si="11"/>
+        <v>37</v>
+      </c>
+      <c r="R38" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [37] = {</v>
+      </c>
+      <c r="S38" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490674; </v>
+      </c>
+      <c r="T38" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490674; </v>
+      </c>
+      <c r="U38" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V38" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W38" t="e">
+        <f>VLOOKUP(D38,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X38" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y38" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z38" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA38" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB38" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC38" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD38" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE38" t="e">
+        <f>VLOOKUP(I38,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF38" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG38" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH38" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Evendim"; }; </v>
+      </c>
+      <c r="AI38" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ38" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK38" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL38" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>1879490643</v>
+      </c>
+      <c r="C39" t="s">
+        <v>203</v>
+      </c>
+      <c r="L39">
+        <v>1</v>
+      </c>
+      <c r="O39" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [38] = {["ID"] = 1879490643; }; -- Birds of Evendim: Common and Uncommon</v>
+      </c>
+      <c r="P39" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q39">
+        <f t="shared" si="11"/>
+        <v>38</v>
+      </c>
+      <c r="R39" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [38] = {</v>
+      </c>
+      <c r="S39" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490643; </v>
+      </c>
+      <c r="T39" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490643; </v>
+      </c>
+      <c r="U39" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V39" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W39" t="e">
+        <f>VLOOKUP(D39,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X39" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y39" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z39" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA39" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB39" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC39" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD39" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE39" t="e">
+        <f>VLOOKUP(I39,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF39" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG39" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH39" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Evendim: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AI39" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ39" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK39" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL39" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>1879490638</v>
+      </c>
+      <c r="C40" t="s">
+        <v>204</v>
+      </c>
+      <c r="L40">
+        <v>2</v>
+      </c>
+      <c r="O40" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [39] = {["ID"] = 1879490638; }; -- Birds of Evendim: Rare</v>
+      </c>
+      <c r="P40" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q40">
+        <f t="shared" si="11"/>
+        <v>39</v>
+      </c>
+      <c r="R40" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [39] = {</v>
+      </c>
+      <c r="S40" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490638; </v>
+      </c>
+      <c r="T40" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490638; </v>
+      </c>
+      <c r="U40" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V40" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W40" t="e">
+        <f>VLOOKUP(D40,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X40" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y40" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z40" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA40" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB40" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC40" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD40" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE40" t="e">
+        <f>VLOOKUP(I40,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF40" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG40" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 2; </v>
+      </c>
+      <c r="AH40" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Evendim: Rare"; }; </v>
+      </c>
+      <c r="AI40" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ40" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK40" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL40" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>1879490615</v>
+      </c>
+      <c r="C41" t="s">
+        <v>205</v>
+      </c>
+      <c r="L41">
+        <v>3</v>
+      </c>
+      <c r="O41" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [40] = {["ID"] = 1879490615; }; -- The Rarest Bird in Evendim</v>
+      </c>
+      <c r="P41" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q41">
+        <f t="shared" si="11"/>
+        <v>40</v>
+      </c>
+      <c r="R41" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [40] = {</v>
+      </c>
+      <c r="S41" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490615; </v>
+      </c>
+      <c r="T41" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490615; </v>
+      </c>
+      <c r="U41" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V41" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W41" t="e">
+        <f>VLOOKUP(D41,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X41" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y41" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z41" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA41" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB41" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC41" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD41" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE41" t="e">
+        <f>VLOOKUP(I41,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF41" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG41" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 3; </v>
+      </c>
+      <c r="AH41" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Evendim"; }; </v>
+      </c>
+      <c r="AI41" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ41" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK41" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL41" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>1879490664</v>
+      </c>
+      <c r="C42" t="s">
+        <v>206</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="O42" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [41] = {["ID"] = 1879490664; }; -- All the Birds of Angmar</v>
+      </c>
+      <c r="P42" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q42">
+        <f t="shared" si="11"/>
+        <v>41</v>
+      </c>
+      <c r="R42" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [41] = {</v>
+      </c>
+      <c r="S42" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490664; </v>
+      </c>
+      <c r="T42" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490664; </v>
+      </c>
+      <c r="U42" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V42" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W42" t="e">
+        <f>VLOOKUP(D42,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X42" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y42" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z42" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA42" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB42" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC42" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD42" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE42" t="e">
+        <f>VLOOKUP(I42,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF42" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG42" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH42" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Angmar"; }; </v>
+      </c>
+      <c r="AI42" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ42" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK42" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL42" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>1879490646</v>
+      </c>
+      <c r="C43" t="s">
+        <v>207</v>
+      </c>
+      <c r="L43">
+        <v>1</v>
+      </c>
+      <c r="O43" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [42] = {["ID"] = 1879490646; }; -- Birds of Angmar: Common and Uncommon</v>
+      </c>
+      <c r="P43" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q43">
+        <f t="shared" si="11"/>
+        <v>42</v>
+      </c>
+      <c r="R43" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [42] = {</v>
+      </c>
+      <c r="S43" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490646; </v>
+      </c>
+      <c r="T43" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490646; </v>
+      </c>
+      <c r="U43" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V43" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W43" t="e">
+        <f>VLOOKUP(D43,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X43" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y43" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z43" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA43" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB43" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC43" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD43" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE43" t="e">
+        <f>VLOOKUP(I43,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF43" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG43" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH43" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Angmar: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AI43" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ43" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK43" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL43" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>1879490636</v>
+      </c>
+      <c r="C44" t="s">
+        <v>208</v>
+      </c>
+      <c r="L44">
+        <v>2</v>
+      </c>
+      <c r="O44" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [43] = {["ID"] = 1879490636; }; -- Birds of Angmar: Rare</v>
+      </c>
+      <c r="P44" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q44">
+        <f t="shared" si="11"/>
+        <v>43</v>
+      </c>
+      <c r="R44" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [43] = {</v>
+      </c>
+      <c r="S44" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490636; </v>
+      </c>
+      <c r="T44" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490636; </v>
+      </c>
+      <c r="U44" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V44" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W44" t="e">
+        <f>VLOOKUP(D44,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X44" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y44" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z44" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA44" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB44" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC44" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD44" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE44" t="e">
+        <f>VLOOKUP(I44,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF44" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG44" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 2; </v>
+      </c>
+      <c r="AH44" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Angmar: Rare"; }; </v>
+      </c>
+      <c r="AI44" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ44" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK44" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL44" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>1879490648</v>
+      </c>
+      <c r="C45" t="s">
+        <v>209</v>
+      </c>
+      <c r="L45">
+        <v>3</v>
+      </c>
+      <c r="O45" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [44] = {["ID"] = 1879490648; }; -- The Rarest Bird in Angmar</v>
+      </c>
+      <c r="P45" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q45">
+        <f t="shared" si="11"/>
+        <v>44</v>
+      </c>
+      <c r="R45" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [44] = {</v>
+      </c>
+      <c r="S45" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490648; </v>
+      </c>
+      <c r="T45" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490648; </v>
+      </c>
+      <c r="U45" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V45" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W45" t="e">
+        <f>VLOOKUP(D45,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X45" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y45" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z45" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA45" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB45" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC45" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD45" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE45" t="e">
+        <f>VLOOKUP(I45,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF45" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG45" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 3; </v>
+      </c>
+      <c r="AH45" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Angmar"; }; </v>
+      </c>
+      <c r="AI45" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ45" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK45" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL45" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>1879490680</v>
+      </c>
+      <c r="C46" t="s">
+        <v>210</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="O46" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [45] = {["ID"] = 1879490680; }; -- All the Birds of Forochel</v>
+      </c>
+      <c r="P46" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q46">
+        <f t="shared" si="11"/>
+        <v>45</v>
+      </c>
+      <c r="R46" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [45] = {</v>
+      </c>
+      <c r="S46" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490680; </v>
+      </c>
+      <c r="T46" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490680; </v>
+      </c>
+      <c r="U46" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V46" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W46" t="e">
+        <f>VLOOKUP(D46,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X46" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y46" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z46" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA46" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB46" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC46" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD46" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE46" t="e">
+        <f>VLOOKUP(I46,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF46" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG46" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH46" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Forochel"; }; </v>
+      </c>
+      <c r="AI46" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ46" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK46" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL46" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>1879490613</v>
+      </c>
+      <c r="C47" t="s">
+        <v>211</v>
+      </c>
+      <c r="L47">
+        <v>1</v>
+      </c>
+      <c r="O47" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [46] = {["ID"] = 1879490613; }; -- Birds of Forochel: Common and Uncommon</v>
+      </c>
+      <c r="P47" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q47">
+        <f t="shared" si="11"/>
+        <v>46</v>
+      </c>
+      <c r="R47" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [46] = {</v>
+      </c>
+      <c r="S47" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490613; </v>
+      </c>
+      <c r="T47" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490613; </v>
+      </c>
+      <c r="U47" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V47" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W47" t="e">
+        <f>VLOOKUP(D47,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X47" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y47" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z47" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA47" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB47" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC47" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD47" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE47" t="e">
+        <f>VLOOKUP(I47,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF47" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG47" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH47" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Forochel: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AI47" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ47" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK47" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL47" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>1879490624</v>
+      </c>
+      <c r="C48" t="s">
+        <v>212</v>
+      </c>
+      <c r="L48">
+        <v>2</v>
+      </c>
+      <c r="O48" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [47] = {["ID"] = 1879490624; }; -- Birds of Forochel: Rare</v>
+      </c>
+      <c r="P48" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q48">
+        <f t="shared" si="11"/>
+        <v>47</v>
+      </c>
+      <c r="R48" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [47] = {</v>
+      </c>
+      <c r="S48" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490624; </v>
+      </c>
+      <c r="T48" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490624; </v>
+      </c>
+      <c r="U48" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V48" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W48" t="e">
+        <f>VLOOKUP(D48,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X48" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y48" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z48" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA48" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB48" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC48" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD48" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE48" t="e">
+        <f>VLOOKUP(I48,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF48" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG48" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 2; </v>
+      </c>
+      <c r="AH48" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Forochel: Rare"; }; </v>
+      </c>
+      <c r="AI48" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ48" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK48" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL48" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="49" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>1879490618</v>
+      </c>
+      <c r="C49" t="s">
+        <v>213</v>
+      </c>
+      <c r="L49">
+        <v>3</v>
+      </c>
+      <c r="O49" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [48] = {["ID"] = 1879490618; }; -- The Rarest Bird in Forochel</v>
+      </c>
+      <c r="P49" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q49">
+        <f t="shared" si="11"/>
+        <v>48</v>
+      </c>
+      <c r="R49" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [48] = {</v>
+      </c>
+      <c r="S49" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490618; </v>
+      </c>
+      <c r="T49" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490618; </v>
+      </c>
+      <c r="U49" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V49" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W49" t="e">
+        <f>VLOOKUP(D49,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X49" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y49" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z49" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA49" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB49" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC49" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD49" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE49" t="e">
+        <f>VLOOKUP(I49,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF49" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG49" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 3; </v>
+      </c>
+      <c r="AH49" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Forochel"; }; </v>
+      </c>
+      <c r="AI49" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ49" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK49" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL49" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>1879490681</v>
+      </c>
+      <c r="C50" t="s">
+        <v>214</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="O50" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [49] = {["ID"] = 1879490681; }; -- All the Birds of Eregion</v>
+      </c>
+      <c r="P50" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q50">
+        <f t="shared" si="11"/>
+        <v>49</v>
+      </c>
+      <c r="R50" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [49] = {</v>
+      </c>
+      <c r="S50" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490681; </v>
+      </c>
+      <c r="T50" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490681; </v>
+      </c>
+      <c r="U50" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V50" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W50" t="e">
+        <f>VLOOKUP(D50,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X50" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y50" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z50" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA50" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB50" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC50" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD50" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE50" t="e">
+        <f>VLOOKUP(I50,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF50" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG50" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH50" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Eregion"; }; </v>
+      </c>
+      <c r="AI50" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ50" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK50" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL50" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="51" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>1879490631</v>
+      </c>
+      <c r="C51" t="s">
+        <v>215</v>
+      </c>
+      <c r="L51">
+        <v>1</v>
+      </c>
+      <c r="O51" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [50] = {["ID"] = 1879490631; }; -- Birds of Eregion: Common and Uncommon</v>
+      </c>
+      <c r="P51" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q51">
+        <f t="shared" si="11"/>
+        <v>50</v>
+      </c>
+      <c r="R51" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [50] = {</v>
+      </c>
+      <c r="S51" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490631; </v>
+      </c>
+      <c r="T51" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490631; </v>
+      </c>
+      <c r="U51" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V51" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W51" t="e">
+        <f>VLOOKUP(D51,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X51" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y51" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z51" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA51" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB51" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC51" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD51" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE51" t="e">
+        <f>VLOOKUP(I51,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF51" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG51" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH51" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Eregion: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AI51" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ51" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK51" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL51" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="52" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>1879490644</v>
+      </c>
+      <c r="C52" t="s">
+        <v>216</v>
+      </c>
+      <c r="L52">
+        <v>2</v>
+      </c>
+      <c r="O52" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [51] = {["ID"] = 1879490644; }; -- Birds of Eregion: Rare</v>
+      </c>
+      <c r="P52" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q52">
+        <f t="shared" si="11"/>
+        <v>51</v>
+      </c>
+      <c r="R52" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [51] = {</v>
+      </c>
+      <c r="S52" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490644; </v>
+      </c>
+      <c r="T52" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490644; </v>
+      </c>
+      <c r="U52" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V52" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W52" t="e">
+        <f>VLOOKUP(D52,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X52" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y52" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z52" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA52" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB52" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC52" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD52" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE52" t="e">
+        <f>VLOOKUP(I52,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF52" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG52" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 2; </v>
+      </c>
+      <c r="AH52" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Eregion: Rare"; }; </v>
+      </c>
+      <c r="AI52" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ52" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK52" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL52" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="53" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>1879490628</v>
+      </c>
+      <c r="C53" t="s">
+        <v>217</v>
+      </c>
+      <c r="L53">
+        <v>3</v>
+      </c>
+      <c r="O53" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [52] = {["ID"] = 1879490628; }; -- The Rarest Bird in Eregion</v>
+      </c>
+      <c r="P53" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q53">
+        <f t="shared" si="11"/>
+        <v>52</v>
+      </c>
+      <c r="R53" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [52] = {</v>
+      </c>
+      <c r="S53" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490628; </v>
+      </c>
+      <c r="T53" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490628; </v>
+      </c>
+      <c r="U53" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V53" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W53" t="e">
+        <f>VLOOKUP(D53,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X53" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y53" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z53" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA53" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB53" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC53" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD53" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE53" t="e">
+        <f>VLOOKUP(I53,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF53" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG53" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 3; </v>
+      </c>
+      <c r="AH53" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Eregion"; }; </v>
+      </c>
+      <c r="AI53" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ53" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK53" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL53" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="54" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>1879490669</v>
+      </c>
+      <c r="C54" t="s">
+        <v>218</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="O54" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [53] = {["ID"] = 1879490669; }; -- All the Birds of Enedwaith</v>
+      </c>
+      <c r="P54" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q54">
+        <f t="shared" si="11"/>
+        <v>53</v>
+      </c>
+      <c r="R54" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [53] = {</v>
+      </c>
+      <c r="S54" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490669; </v>
+      </c>
+      <c r="T54" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490669; </v>
+      </c>
+      <c r="U54" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V54" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W54" t="e">
+        <f>VLOOKUP(D54,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X54" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y54" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z54" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA54" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB54" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC54" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD54" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE54" t="e">
+        <f>VLOOKUP(I54,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF54" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG54" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH54" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Enedwaith"; }; </v>
+      </c>
+      <c r="AI54" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ54" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK54" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL54" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="55" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>1879490616</v>
+      </c>
+      <c r="C55" t="s">
+        <v>219</v>
+      </c>
+      <c r="L55">
+        <v>1</v>
+      </c>
+      <c r="O55" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [54] = {["ID"] = 1879490616; }; -- Birds of Enedwaith: Common and Uncommon</v>
+      </c>
+      <c r="P55" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q55">
+        <f t="shared" si="11"/>
+        <v>54</v>
+      </c>
+      <c r="R55" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [54] = {</v>
+      </c>
+      <c r="S55" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490616; </v>
+      </c>
+      <c r="T55" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490616; </v>
+      </c>
+      <c r="U55" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V55" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W55" t="e">
+        <f>VLOOKUP(D55,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X55" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y55" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z55" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA55" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB55" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC55" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD55" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE55" t="e">
+        <f>VLOOKUP(I55,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF55" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG55" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH55" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Enedwaith: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AI55" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ55" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK55" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL55" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="56" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>1879490652</v>
+      </c>
+      <c r="C56" t="s">
+        <v>220</v>
+      </c>
+      <c r="L56">
+        <v>2</v>
+      </c>
+      <c r="O56" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [55] = {["ID"] = 1879490652; }; -- Birds of Enedwaith: Rare</v>
+      </c>
+      <c r="P56" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q56">
+        <f t="shared" si="11"/>
+        <v>55</v>
+      </c>
+      <c r="R56" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [55] = {</v>
+      </c>
+      <c r="S56" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490652; </v>
+      </c>
+      <c r="T56" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490652; </v>
+      </c>
+      <c r="U56" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V56" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W56" t="e">
+        <f>VLOOKUP(D56,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X56" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y56" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z56" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA56" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB56" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC56" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD56" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE56" t="e">
+        <f>VLOOKUP(I56,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF56" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG56" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 2; </v>
+      </c>
+      <c r="AH56" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Enedwaith: Rare"; }; </v>
+      </c>
+      <c r="AI56" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ56" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK56" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL56" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="57" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>1879490653</v>
+      </c>
+      <c r="C57" t="s">
+        <v>221</v>
+      </c>
+      <c r="L57">
+        <v>3</v>
+      </c>
+      <c r="O57" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [56] = {["ID"] = 1879490653; }; -- The Rarest Bird in Enedwaith</v>
+      </c>
+      <c r="P57" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q57">
+        <f t="shared" si="11"/>
+        <v>56</v>
+      </c>
+      <c r="R57" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [56] = {</v>
+      </c>
+      <c r="S57" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490653; </v>
+      </c>
+      <c r="T57" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490653; </v>
+      </c>
+      <c r="U57" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V57" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W57" t="e">
+        <f>VLOOKUP(D57,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X57" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y57" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z57" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA57" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB57" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC57" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD57" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE57" t="e">
+        <f>VLOOKUP(I57,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF57" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG57" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 3; </v>
+      </c>
+      <c r="AH57" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Enedwaith"; }; </v>
+      </c>
+      <c r="AI57" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ57" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK57" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL57" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="58" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>1879490672</v>
+      </c>
+      <c r="C58" t="s">
+        <v>222</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="O58" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [57] = {["ID"] = 1879490672; }; -- All the Birds of Dunland</v>
+      </c>
+      <c r="P58" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q58">
+        <f t="shared" si="11"/>
+        <v>57</v>
+      </c>
+      <c r="R58" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [57] = {</v>
+      </c>
+      <c r="S58" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490672; </v>
+      </c>
+      <c r="T58" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490672; </v>
+      </c>
+      <c r="U58" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V58" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W58" t="e">
+        <f>VLOOKUP(D58,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X58" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y58" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z58" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA58" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB58" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC58" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD58" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE58" t="e">
+        <f>VLOOKUP(I58,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF58" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG58" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH58" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Dunland"; }; </v>
+      </c>
+      <c r="AI58" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ58" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK58" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL58" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="59" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>1879490623</v>
+      </c>
+      <c r="C59" t="s">
+        <v>223</v>
+      </c>
+      <c r="L59">
+        <v>1</v>
+      </c>
+      <c r="O59" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [58] = {["ID"] = 1879490623; }; -- Birds of Dunland: Common and Uncommon</v>
+      </c>
+      <c r="P59" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q59">
+        <f t="shared" si="11"/>
+        <v>58</v>
+      </c>
+      <c r="R59" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [58] = {</v>
+      </c>
+      <c r="S59" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490623; </v>
+      </c>
+      <c r="T59" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490623; </v>
+      </c>
+      <c r="U59" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V59" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W59" t="e">
+        <f>VLOOKUP(D59,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X59" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y59" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z59" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA59" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB59" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC59" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD59" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE59" t="e">
+        <f>VLOOKUP(I59,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF59" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG59" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH59" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Dunland: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AI59" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ59" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK59" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL59" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="60" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>1879490634</v>
+      </c>
+      <c r="C60" t="s">
+        <v>224</v>
+      </c>
+      <c r="L60">
+        <v>2</v>
+      </c>
+      <c r="O60" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [59] = {["ID"] = 1879490634; }; -- Birds of Dunland: Rare</v>
+      </c>
+      <c r="P60" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q60">
+        <f t="shared" si="11"/>
+        <v>59</v>
+      </c>
+      <c r="R60" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [59] = {</v>
+      </c>
+      <c r="S60" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490634; </v>
+      </c>
+      <c r="T60" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490634; </v>
+      </c>
+      <c r="U60" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V60" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W60" t="e">
+        <f>VLOOKUP(D60,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X60" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y60" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z60" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA60" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB60" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC60" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD60" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE60" t="e">
+        <f>VLOOKUP(I60,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF60" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG60" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 2; </v>
+      </c>
+      <c r="AH60" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Dunland: Rare"; }; </v>
+      </c>
+      <c r="AI60" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ60" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK60" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL60" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="61" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>1879490619</v>
+      </c>
+      <c r="C61" t="s">
+        <v>225</v>
+      </c>
+      <c r="L61">
+        <v>3</v>
+      </c>
+      <c r="O61" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [60] = {["ID"] = 1879490619; }; -- The Rarest Bird in Dunland</v>
+      </c>
+      <c r="P61" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q61">
+        <f t="shared" si="11"/>
+        <v>60</v>
+      </c>
+      <c r="R61" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [60] = {</v>
+      </c>
+      <c r="S61" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490619; </v>
+      </c>
+      <c r="T61" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490619; </v>
+      </c>
+      <c r="U61" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V61" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W61" t="e">
+        <f>VLOOKUP(D61,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X61" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y61" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z61" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA61" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB61" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC61" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD61" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE61" t="e">
+        <f>VLOOKUP(I61,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF61" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG61" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 3; </v>
+      </c>
+      <c r="AH61" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Dunland"; }; </v>
+      </c>
+      <c r="AI61" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ61" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK61" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL61" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="62" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>1879490679</v>
+      </c>
+      <c r="C62" t="s">
+        <v>230</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="O62" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [61] = {["ID"] = 1879490679; }; -- The Rarest of Birds in Eriador</v>
+      </c>
+      <c r="P62" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q62">
+        <f t="shared" si="11"/>
+        <v>61</v>
+      </c>
+      <c r="R62" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [61] = {</v>
+      </c>
+      <c r="S62" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">["ID"] = 1879490679; </v>
+      </c>
+      <c r="T62" t="str">
+        <f t="shared" si="14"/>
+        <v xml:space="preserve">["ID"] = 1879490679; </v>
+      </c>
+      <c r="U62" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V62" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W62" t="e">
+        <f>VLOOKUP(D62,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X62" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y62" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z62" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA62" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB62" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC62" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD62" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE62" t="e">
+        <f>VLOOKUP(I62,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF62" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG62" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH62" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest of Birds in Eriador"; }; </v>
+      </c>
+      <c r="AI62" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ62" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK62" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL62" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="63" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="O63" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [62] = {}; -- </v>
+      </c>
+      <c r="P63" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q63">
+        <f t="shared" si="11"/>
+        <v>62</v>
+      </c>
+      <c r="R63" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [62] = {</v>
+      </c>
+      <c r="S63" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="T63" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="U63" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V63" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W63" t="e">
+        <f>VLOOKUP(D63,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X63" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y63" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z63" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA63" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB63" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC63" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD63" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE63" t="e">
+        <f>VLOOKUP(I63,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF63" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG63" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH63" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AI63" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ63" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK63" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL63" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="64" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="O64" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [63] = {}; -- </v>
+      </c>
+      <c r="P64" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q64">
+        <f t="shared" si="11"/>
+        <v>63</v>
+      </c>
+      <c r="R64" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [63] = {</v>
+      </c>
+      <c r="S64" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="T64" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="U64" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V64" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W64" t="e">
+        <f>VLOOKUP(D64,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X64" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y64" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z64" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA64" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB64" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC64" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD64" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE64" t="e">
+        <f>VLOOKUP(I64,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF64" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG64" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH64" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AI64" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ64" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK64" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL64" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="65" spans="15:38" x14ac:dyDescent="0.25">
+      <c r="O65" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [64] = {}; -- </v>
+      </c>
+      <c r="P65" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q65">
+        <f t="shared" si="11"/>
+        <v>64</v>
+      </c>
+      <c r="R65" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [64] = {</v>
+      </c>
+      <c r="S65" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="T65" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="U65" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V65" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W65" t="e">
+        <f>VLOOKUP(D65,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X65" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y65" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z65" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA65" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB65" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC65" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD65" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE65" t="e">
+        <f>VLOOKUP(I65,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF65" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG65" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH65" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AI65" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ65" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK65" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL65" t="str">
+        <f t="shared" si="30"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="66" spans="15:38" x14ac:dyDescent="0.25">
+      <c r="O66" t="str">
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> [65] = {}; -- </v>
+      </c>
+      <c r="P66" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q66">
+        <f t="shared" si="11"/>
+        <v>65</v>
+      </c>
+      <c r="R66" t="str">
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> [65] = {</v>
+      </c>
+      <c r="S66" t="str">
+        <f t="shared" si="13"/>
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="T66" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="U66" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V66" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W66" t="e">
+        <f>VLOOKUP(D66,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X66" t="e">
+        <f t="shared" si="17"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y66" t="str">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Z66" t="str">
+        <f t="shared" si="19"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA66" t="str">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AB66" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC66" t="str">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AD66" t="str">
+        <f t="shared" si="23"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE66" t="e">
+        <f>VLOOKUP(I66,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF66" t="e">
+        <f t="shared" si="24"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG66" t="str">
+        <f t="shared" si="25"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH66" t="str">
+        <f t="shared" si="26"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AI66" t="str">
+        <f t="shared" si="27"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ66" t="str">
+        <f t="shared" si="28"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK66" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL66" t="str">
+        <f t="shared" si="30"/>
         <v>};</v>
       </c>
     </row>
@@ -2850,7 +10123,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4334862E-8819-4206-A9EF-507FA6D3D8A8}">
   <dimension ref="A1:AK36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/SourceFiles/DeedInfo-3-Hobbies.xlsx
+++ b/SourceFiles/DeedInfo-3-Hobbies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkckx\Documents\The Lord of the Rings Online\Plugins\CubePlugins\DeedTracker\SourceFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7CF0A0D-3990-4582-A8F4-C316E1F42EDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EAB468D-9FF4-47EB-B101-0255172A678F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1290" yWindow="1860" windowWidth="19665" windowHeight="12690" activeTab="6" xr2:uid="{CDC9C16A-58F0-4807-B5CD-F77FF9D2EA43}"/>
+    <workbookView xWindow="-17925" yWindow="0" windowWidth="13620" windowHeight="15600" activeTab="6" xr2:uid="{CDC9C16A-58F0-4807-B5CD-F77FF9D2EA43}"/>
   </bookViews>
   <sheets>
     <sheet name="Type" sheetId="2" r:id="rId1"/>
@@ -3195,7 +3195,7 @@
         <v xml:space="preserve">  [1] = {["ID"] = 1879490678; }; -- All the Birds of Bree-land</v>
       </c>
       <c r="P2" s="1" t="e">
-        <f t="shared" ref="P2:P7" si="0">CONCATENATE(R2,S2,V2,X2,Z2,AB2,AD2,AF2,AG2,AH2,AI2,AJ2,AK2,AL2)</f>
+        <f t="shared" ref="P2" si="0">CONCATENATE(R2,S2,V2,X2,Z2,AB2,AD2,AF2,AG2,AH2,AI2,AJ2,AK2,AL2)</f>
         <v>#N/A</v>
       </c>
       <c r="Q2">
@@ -3207,19 +3207,19 @@
         <v xml:space="preserve">  [1] = {</v>
       </c>
       <c r="S2" t="str">
-        <f t="shared" ref="S2:S7" si="1">IF(LEN(A2)&gt;0,CONCATENATE("[""ID""] = ",A2,"; "),"                     ")</f>
+        <f t="shared" ref="S2" si="1">IF(LEN(A2)&gt;0,CONCATENATE("[""ID""] = ",A2,"; "),"                     ")</f>
         <v xml:space="preserve">["ID"] = 1879490678; </v>
       </c>
       <c r="T2" t="str">
-        <f t="shared" ref="T2:T7" si="2">IF(LEN(A2)&gt;0,CONCATENATE("[""ID""] = ",A2,"; "),"")</f>
+        <f t="shared" ref="T2" si="2">IF(LEN(A2)&gt;0,CONCATENATE("[""ID""] = ",A2,"; "),"")</f>
         <v xml:space="preserve">["ID"] = 1879490678; </v>
       </c>
       <c r="U2" t="str">
-        <f t="shared" ref="U2:U7" si="3">IF(LEN(M2)&gt;0,CONCATENATE("[""CAT_ID""] = ",M2,"; "),"")</f>
+        <f t="shared" ref="U2" si="3">IF(LEN(M2)&gt;0,CONCATENATE("[""CAT_ID""] = ",M2,"; "),"")</f>
         <v/>
       </c>
       <c r="V2" s="1" t="str">
-        <f t="shared" ref="V2:V7" si="4">IF(LEN(B2)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B2)),B2,"; "),"")</f>
+        <f t="shared" ref="V2" si="4">IF(LEN(B2)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B2)),B2,"; "),"")</f>
         <v/>
       </c>
       <c r="W2" t="e">
@@ -3231,7 +3231,7 @@
         <v>#N/A</v>
       </c>
       <c r="Y2" t="str">
-        <f t="shared" ref="Y2:Y7" si="5">TEXT(E2,0)</f>
+        <f t="shared" ref="Y2" si="5">TEXT(E2,0)</f>
         <v>0</v>
       </c>
       <c r="Z2" t="str">
@@ -3239,7 +3239,7 @@
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AA2" t="str">
-        <f t="shared" ref="AA2:AA7" si="6">TEXT(G2,0)</f>
+        <f t="shared" ref="AA2" si="6">TEXT(G2,0)</f>
         <v>0</v>
       </c>
       <c r="AB2" t="str">
@@ -3247,7 +3247,7 @@
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AC2" t="str">
-        <f t="shared" ref="AC2:AC7" si="7">TEXT(H2,0)</f>
+        <f t="shared" ref="AC2" si="7">TEXT(H2,0)</f>
         <v>0</v>
       </c>
       <c r="AD2" t="str">
@@ -3259,7 +3259,7 @@
         <v>1</v>
       </c>
       <c r="AF2" t="str">
-        <f t="shared" ref="AF2:AF7" si="8">CONCATENATE("[""FACTION""] = ",TEXT(AE2,"0"),"; ")</f>
+        <f t="shared" ref="AF2" si="8">CONCATENATE("[""FACTION""] = ",TEXT(AE2,"0"),"; ")</f>
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AG2" t="str">
@@ -3408,7 +3408,7 @@
         <v>79</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O4" t="str">
         <f t="shared" si="9"/>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="AG4" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 2; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH4" t="str">
         <f t="shared" si="26"/>
@@ -3518,7 +3518,7 @@
         <v>79</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O5" t="str">
         <f t="shared" si="9"/>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AG5" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 3; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH5" t="str">
         <f t="shared" si="26"/>
@@ -3845,7 +3845,7 @@
         <v>176</v>
       </c>
       <c r="L8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8" t="str">
         <f t="shared" si="9"/>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="AG8" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 2; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH8" t="str">
         <f t="shared" si="26"/>
@@ -3952,7 +3952,7 @@
         <v>175</v>
       </c>
       <c r="L9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O9" t="str">
         <f t="shared" si="9"/>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="AG9" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 3; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH9" t="str">
         <f t="shared" si="26"/>
@@ -4273,7 +4273,7 @@
         <v>180</v>
       </c>
       <c r="L12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O12" t="str">
         <f t="shared" si="9"/>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="AG12" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 2; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH12" t="str">
         <f t="shared" si="26"/>
@@ -4380,7 +4380,7 @@
         <v>179</v>
       </c>
       <c r="L13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O13" t="str">
         <f t="shared" si="9"/>
@@ -4456,7 +4456,7 @@
       </c>
       <c r="AG13" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 3; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH13" t="str">
         <f t="shared" si="26"/>
@@ -4701,7 +4701,7 @@
         <v>184</v>
       </c>
       <c r="L16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O16" t="str">
         <f t="shared" si="9"/>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="AG16" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 2; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH16" t="str">
         <f t="shared" si="26"/>
@@ -4808,7 +4808,7 @@
         <v>185</v>
       </c>
       <c r="L17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O17" t="str">
         <f t="shared" si="9"/>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG17" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 3; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH17" t="str">
         <f t="shared" si="26"/>
@@ -5129,7 +5129,7 @@
         <v>228</v>
       </c>
       <c r="L20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O20" t="str">
         <f t="shared" si="9"/>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="AG20" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 2; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH20" t="str">
         <f t="shared" si="26"/>
@@ -5236,7 +5236,7 @@
         <v>229</v>
       </c>
       <c r="L21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O21" t="str">
         <f t="shared" si="9"/>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="AG21" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 3; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH21" t="str">
         <f t="shared" si="26"/>
@@ -5557,7 +5557,7 @@
         <v>188</v>
       </c>
       <c r="L24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O24" t="str">
         <f t="shared" si="9"/>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="AG24" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 2; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH24" t="str">
         <f t="shared" si="26"/>
@@ -5664,7 +5664,7 @@
         <v>189</v>
       </c>
       <c r="L25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O25" t="str">
         <f t="shared" si="9"/>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="AG25" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 3; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH25" t="str">
         <f t="shared" si="26"/>
@@ -5985,7 +5985,7 @@
         <v>192</v>
       </c>
       <c r="L28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O28" t="str">
         <f t="shared" si="9"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="AG28" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 2; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH28" t="str">
         <f t="shared" si="26"/>
@@ -6092,7 +6092,7 @@
         <v>193</v>
       </c>
       <c r="L29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O29" t="str">
         <f t="shared" si="9"/>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="AG29" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 3; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH29" t="str">
         <f t="shared" si="26"/>
@@ -6413,7 +6413,7 @@
         <v>196</v>
       </c>
       <c r="L32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O32" t="str">
         <f t="shared" si="9"/>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="AG32" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 2; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH32" t="str">
         <f t="shared" si="26"/>
@@ -6520,7 +6520,7 @@
         <v>197</v>
       </c>
       <c r="L33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O33" t="str">
         <f t="shared" si="9"/>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="AG33" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 3; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH33" t="str">
         <f t="shared" si="26"/>
@@ -6841,7 +6841,7 @@
         <v>200</v>
       </c>
       <c r="L36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O36" t="str">
         <f t="shared" si="9"/>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AG36" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 2; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH36" t="str">
         <f t="shared" si="26"/>
@@ -6948,7 +6948,7 @@
         <v>201</v>
       </c>
       <c r="L37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O37" t="str">
         <f t="shared" si="9"/>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="AG37" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 3; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH37" t="str">
         <f t="shared" si="26"/>
@@ -7269,7 +7269,7 @@
         <v>204</v>
       </c>
       <c r="L40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O40" t="str">
         <f t="shared" si="9"/>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="AG40" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 2; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH40" t="str">
         <f t="shared" si="26"/>
@@ -7376,7 +7376,7 @@
         <v>205</v>
       </c>
       <c r="L41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O41" t="str">
         <f t="shared" si="9"/>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="AG41" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 3; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH41" t="str">
         <f t="shared" si="26"/>
@@ -7697,7 +7697,7 @@
         <v>208</v>
       </c>
       <c r="L44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O44" t="str">
         <f t="shared" si="9"/>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="AG44" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 2; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH44" t="str">
         <f t="shared" si="26"/>
@@ -7804,7 +7804,7 @@
         <v>209</v>
       </c>
       <c r="L45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O45" t="str">
         <f t="shared" si="9"/>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="AG45" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 3; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH45" t="str">
         <f t="shared" si="26"/>
@@ -8125,7 +8125,7 @@
         <v>212</v>
       </c>
       <c r="L48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O48" t="str">
         <f t="shared" si="9"/>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="AG48" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 2; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH48" t="str">
         <f t="shared" si="26"/>
@@ -8232,7 +8232,7 @@
         <v>213</v>
       </c>
       <c r="L49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O49" t="str">
         <f t="shared" si="9"/>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="AG49" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 3; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH49" t="str">
         <f t="shared" si="26"/>
@@ -8553,7 +8553,7 @@
         <v>216</v>
       </c>
       <c r="L52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O52" t="str">
         <f t="shared" si="9"/>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="AG52" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 2; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH52" t="str">
         <f t="shared" si="26"/>
@@ -8660,7 +8660,7 @@
         <v>217</v>
       </c>
       <c r="L53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O53" t="str">
         <f t="shared" si="9"/>
@@ -8736,7 +8736,7 @@
       </c>
       <c r="AG53" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 3; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH53" t="str">
         <f t="shared" si="26"/>
@@ -8981,7 +8981,7 @@
         <v>220</v>
       </c>
       <c r="L56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O56" t="str">
         <f t="shared" si="9"/>
@@ -9057,7 +9057,7 @@
       </c>
       <c r="AG56" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 2; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH56" t="str">
         <f t="shared" si="26"/>
@@ -9088,7 +9088,7 @@
         <v>221</v>
       </c>
       <c r="L57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O57" t="str">
         <f t="shared" si="9"/>
@@ -9164,7 +9164,7 @@
       </c>
       <c r="AG57" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 3; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH57" t="str">
         <f t="shared" si="26"/>
@@ -9409,7 +9409,7 @@
         <v>224</v>
       </c>
       <c r="L60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O60" t="str">
         <f t="shared" si="9"/>
@@ -9485,7 +9485,7 @@
       </c>
       <c r="AG60" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 2; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH60" t="str">
         <f t="shared" si="26"/>
@@ -9516,7 +9516,7 @@
         <v>225</v>
       </c>
       <c r="L61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O61" t="str">
         <f t="shared" si="9"/>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="AG61" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 3; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH61" t="str">
         <f t="shared" si="26"/>
